--- a/output/full_scan/batch_seq3_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq3_2026-09-24.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1100.082391120078</v>
+        <v>1100.082391120077</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>119.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.35916911474783</v>
+        <v>67.35916913022429</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.979840720392</v>
+        <v>31.97984075438159</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.673234644587856</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.447133789627729</v>
+        <v>1.447133789504097</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>84.20044562149066</v>
+        <v>84.20044562378624</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.24541069960232</v>
+        <v>31.24541071178341</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.193580447083624</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.170439483999535</v>
+        <v>5.170439484051052</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.87252202206318</v>
+        <v>63.87252199904209</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.27645974342271</v>
+        <v>12.27645977317179</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3.118061260819318</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.164259126557275</v>
+        <v>2.164259126577903</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.38368042222203</v>
+        <v>68.38368042998331</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.18342024421135</v>
+        <v>18.18342025045289</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.7299822735647015</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>21.70405307780466</v>
+        <v>21.70405307708353</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>77.37795193725816</v>
+        <v>77.37795194013464</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>40.97035182343127</v>
+        <v>40.97035183197509</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.9879942208468172</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>73.79047158181011</v>
+        <v>73.79047159679217</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.22731099308628</v>
+        <v>30.22731104692292</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.8876246206235756</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>63.78141625135854</v>
+        <v>63.78141624723742</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.47202487231529</v>
+        <v>59.47202487315005</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.38837743914452</v>
+        <v>20.38837741342502</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.25730677294057</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.769731796213708</v>
+        <v>2.769731796254845</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>973.7590327297446</v>
+        <v>973.7590327297444</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>15.45</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>73.32187856750627</v>
+        <v>73.32187868809459</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>54.04532293027849</v>
+        <v>54.04532288050641</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>4.967729596012565</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0766607972434656</v>
+        <v>0.0766607972022554</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>69.61414714966475</v>
+        <v>69.61414719240109</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.64512128990399</v>
+        <v>19.64512125759297</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.212851387665661</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.739771419802849</v>
+        <v>3.739771419493755</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>73.96907367962966</v>
+        <v>73.96907369390064</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>26.00189199980414</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.37860025039184</v>
+        <v>60.37860023843704</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>18.93591435853957</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0749558788746965</v>
+        <v>0.0749558789571195</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.89602077894379</v>
+        <v>63.89602078156517</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.17909779523387</v>
+        <v>21.17909778673937</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.6718090943420125</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.479871943081527</v>
+        <v>2.479871943040244</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>67.89175037128554</v>
+        <v>67.89175037465733</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.55489951521559</v>
+        <v>41.55489951616129</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.092277299122219</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.119965501185683</v>
+        <v>1.119965501195986</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>877.0419500289253</v>
+        <v>877.041950028925</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>45.15</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>66.28817311402042</v>
+        <v>66.2881730917688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45.56647561415229</v>
+        <v>45.56647560519136</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.3668933933738023</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0368222158961628</v>
+        <v>0.0368222159991882</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>57.30918122553471</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.87256556033915</v>
+        <v>34.87256554378452</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.2796491076966693</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.926377072691</v>
+        <v>64.92637705377061</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>54.36731956068336</v>
+        <v>54.36731955234778</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.3660903341828601</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1682353414182316</v>
+        <v>-0.1682353413461066</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.13343440568406</v>
+        <v>59.13343433705232</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46.68728135171265</v>
+        <v>46.68728141995782</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.3340836202469773</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.0689245959106288</v>
+        <v>-0.0689245957560817</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>66.40067752981312</v>
+        <v>66.40067753823446</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46.53928447312541</v>
+        <v>46.53928448122154</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.3212201754351927</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.012248587611563</v>
+        <v>0.0122485876527753</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>77.8806405405137</v>
+        <v>77.88064052877513</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>40.25373285553273</v>
+        <v>40.25373284014363</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.788821133866505</v>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>839.8029859503971</v>
+        <v>839.8029859503972</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>3555</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.40481762185365</v>
+        <v>62.40481763350751</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.15496218138481</v>
+        <v>17.1549621678079</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7376549092976042</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-4.686429049093789</v>
+        <v>-4.686429046003269</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>65.60701067755127</v>
+        <v>65.60701070080064</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.55212399266365</v>
+        <v>23.55212400341363</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.8921390607503756</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.336923080047721</v>
+        <v>5.336923079532603</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.0206577540999</v>
+        <v>57.02065774532169</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.637573632152629</v>
+        <v>9.637573600257724</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>4.776461597248758</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.908459309710025</v>
+        <v>2.908459310225171</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.80246136897587</v>
+        <v>58.80246135917142</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>34.13382584366163</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3162972835327773</v>
+        <v>0.3162972839449085</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.29035183648157</v>
+        <v>63.29035184445677</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.72287881470274</v>
+        <v>26.72287881601898</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.8336037653263562</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>68.56974881928198</v>
+        <v>68.56974881166477</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37.01260481053447</v>
+        <v>37.01260481840499</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.4242626749866391</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1430065580185466</v>
+        <v>0.1430065580391487</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.63548615390938</v>
+        <v>56.63548612623081</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.70530164702316</v>
+        <v>37.70530163230243</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.5745505998409098</v>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>781.8559992684575</v>
+        <v>781.8559992684578</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>37.3</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.02429350136781</v>
+        <v>56.02429238980737</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.53234220092354</v>
+        <v>26.53234226830413</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.5857464506086772</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0053402907128006</v>
+        <v>0.0053402907334084</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.63200404858848</v>
+        <v>65.63200395242674</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>44.03839052052936</v>
+        <v>44.03839051999199</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.6078466135900267</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0200817770585359</v>
+        <v>0.0200817772645875</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.03787100717555</v>
+        <v>54.03787099788722</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.2326263627521</v>
+        <v>21.23262634001929</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.8266157303687118</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5900449169465709</v>
+        <v>-0.5900449166993122</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.68173833424567</v>
+        <v>59.68173830645227</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>39.0482429784655</v>
+        <v>39.04824346071764</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>3.448151378147453</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0340294752520094</v>
+        <v>-0.0340294751758051</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>734.7641070824941</v>
+        <v>734.7641070824939</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>538</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.70843907164374</v>
+        <v>65.7084390896032</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.74833644143158</v>
+        <v>30.7483364292437</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.4769846008235309</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.437801012194019</v>
+        <v>2.437801011678878</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.28471336174748</v>
+        <v>54.28471339749531</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.46045152404437</v>
+        <v>29.46045149857574</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.2751369455789065</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1408774066896256</v>
+        <v>-0.1408774067926554</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>66.47537522664342</v>
+        <v>66.47537497301997</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.43737715513913</v>
+        <v>34.43737757719676</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6353217541953575</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1192522037686351</v>
+        <v>-0.1192522031800613</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.05103663060684</v>
+        <v>49.05103662537523</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6.746885894422533</v>
+        <v>6.746885923488451</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.130968915394447</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0284632964344547</v>
+        <v>0.0284632964550583</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>699.280658095936</v>
+        <v>699.2806580959359</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>100.5</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.90655515491737</v>
+        <v>57.9065551669526</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41.29653187847006</v>
+        <v>41.29653187313866</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.4982045516824597</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.4682505718161973</v>
+        <v>-0.4682505718986176</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>58.69598003608613</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>42.80766433685585</v>
+        <v>42.80766436637772</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.005977935548722</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2585207001049135</v>
+        <v>0.2585207001461249</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>694.5165867025812</v>
+        <v>694.5165867025813</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>39.05</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>56.12825468749669</v>
+        <v>56.12825463730253</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.60526602225692</v>
+        <v>20.60526606342553</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.6236515273155553</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3191484051524769</v>
+        <v>0.3191484052967197</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.76993626346447</v>
+        <v>46.76993626128969</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.32536387601592</v>
+        <v>18.32536384260998</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.7514507125224493</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.411618711661623</v>
+        <v>2.411618711826481</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.09556881446412</v>
+        <v>53.09556874383137</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.92702870525581</v>
+        <v>24.92702859094246</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.5109684579988553</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0011152528388609</v>
+        <v>0.001115253086128</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>72.90923581921101</v>
+        <v>72.90923582726089</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>45.06807125701642</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>5.24777944702889</v>
+        <v>5.247779446925852</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>64.81979585955204</v>
+        <v>64.81979586832728</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>20.15358691752214</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5870559049724406</v>
+        <v>0.5870559049621462</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>674.8363581429959</v>
+        <v>674.8363581429958</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>140.5</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>64.36623516373663</v>
+        <v>64.36623523882781</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>25.15052493678222</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.298319388776269</v>
+        <v>1.298319388673268</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.13189450789307</v>
+        <v>56.13189454941945</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>35.29499653393964</v>
+        <v>35.29499653393963</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.3263114045187097</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.8946366108093819</v>
+        <v>-0.8946366111390676</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>60.9130329792946</v>
+        <v>60.91303303407285</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.95298808877427</v>
+        <v>19.9529880684167</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.5487289514262077</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0420972835008406</v>
+        <v>-0.0420972841190074</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>58.51130389471941</v>
+        <v>58.51130385479171</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>41.7375858283387</v>
+        <v>41.73758584169226</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.4327569967903438</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0083343783589918</v>
+        <v>-0.008334378346628099</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>61.47641035962519</v>
+        <v>61.47641033516549</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>40.67867153701744</v>
+        <v>40.67867143361326</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.5580046851103763</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1970774193394922</v>
+        <v>-0.1970774192776709</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.53426947896357</v>
+        <v>54.53426938901874</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12.56908561716233</v>
+        <v>12.56908560376613</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>2.556955301050489</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2205986746685699</v>
+        <v>0.2205986750806834</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>633.3245394299462</v>
+        <v>633.3245394299461</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>26.95</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>62.70492622547004</v>
+        <v>62.70492622189055</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.57262665234969</v>
+        <v>29.5726266523497</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.877043670878189</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1833856631765555</v>
+        <v>0.1833856631456493</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.68288333819859</v>
+        <v>54.68288336067212</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>29.74872004788957</v>
+        <v>29.74872005201946</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.173434029982644</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1275764611134103</v>
+        <v>0.1275764611958327</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>61.7405955041265</v>
+        <v>61.74059552302887</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>49.21548353653507</v>
+        <v>49.21548351243336</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.5726301357151715</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0849281708190763</v>
+        <v>-0.0849281708396787</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>625.0193901306292</v>
+        <v>625.0193901306293</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>129.5</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.65241730434099</v>
+        <v>54.65241739512869</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10.76501932436902</v>
+        <v>10.76501941195043</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.7168588642303524</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.919254936699368</v>
+        <v>0.91925493622543</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.67693325218298</v>
+        <v>50.67693326464157</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26.39516869540661</v>
+        <v>26.39516869616953</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.114428752024756</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.7660758595819397</v>
+        <v>-0.7660758599939941</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.44849334408293</v>
+        <v>52.4484933539638</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.96932518254038</v>
+        <v>12.96932515640457</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.5245690437060039</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.662548499027932</v>
+        <v>0.6625484989455073</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>612.0728131090671</v>
+        <v>612.0728131090672</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>42.5</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>59.08004657510688</v>
+        <v>59.08004656023282</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>43.93934304336586</v>
+        <v>43.93934301878588</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3375388084709775</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2367731123057814</v>
+        <v>-0.2367731122542706</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.65613515785084</v>
+        <v>54.65613517605325</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>32.74819233017526</v>
+        <v>32.74819240474837</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.5897709705302236</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0646166673579921</v>
+        <v>-0.06461666740951209</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>65.74730363400623</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>51.74840059184596</v>
+        <v>51.74840057359858</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4187237161791118</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0389592489036041</v>
+        <v>-0.0389592488933014</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>58.40839285175458</v>
+        <v>58.40839283050396</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>50.11875969080614</v>
+        <v>50.11875966251016</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.3825660459611733</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.06865857781031651</v>
+        <v>-0.06865857773819251</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>597.025431091856</v>
+        <v>597.0254310918561</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>150</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>57.21175705607192</v>
+        <v>57.21175702700567</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>35.66884885307532</v>
+        <v>35.66884884514631</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.4813969357462679</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.5258313031662798</v>
+        <v>-0.5258313028778447</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.43818251478224</v>
+        <v>53.4381822730116</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38.26028241630206</v>
+        <v>38.26028241630205</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.1642424133129711</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0010266044369976</v>
+        <v>0.001026604457602</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>54.23745270677644</v>
+        <v>54.23745266667906</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.85420862050513</v>
+        <v>29.85420866066544</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.6626142553186907</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0458551234395702</v>
+        <v>-0.0458551234189655</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>65.39030742416877</v>
+        <v>65.39030737444013</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.53692509051805</v>
+        <v>18.53692513633971</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.8186746019670171</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1812650813161441</v>
+        <v>0.1812650815015961</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>51.04483873514064</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.11064852026324</v>
+        <v>21.11064850021859</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5033120834426517</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-126.9959292030793</v>
+        <v>-126.9959291948374</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.48768472755889</v>
+        <v>53.48768478134322</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>37.44080708094314</v>
+        <v>37.4408071718121</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.3390684969860393</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.4420175370481871</v>
+        <v>-0.4420175373160653</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.07874690035695</v>
+        <v>54.07874674727562</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.47956846561796</v>
+        <v>21.47956845688448</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4695103352807301</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0522716894338426</v>
+        <v>-0.0522716895780821</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>575.0683386352752</v>
+        <v>575.0683386352753</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>212.5</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>35.33888706978672</v>
+        <v>35.3388870173778</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.68602296885635</v>
+        <v>23.68602299646167</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1.488147275173699</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0554415471449099</v>
+        <v>-0.0554415467327595</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>59.35094102203653</v>
+        <v>59.35094101731038</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.98312209420546</v>
+        <v>16.98312206451206</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>3.376848501403539</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4356850995820094</v>
+        <v>0.4356850996232211</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.93238456572059</v>
+        <v>49.93238457347596</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.74391886471522</v>
+        <v>21.74391895480696</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.3859460029097875</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-3.316216138864146</v>
+        <v>-3.316216138905379</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.24153670726403</v>
+        <v>53.24153667533946</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.32630901158131</v>
+        <v>21.32630905884131</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.7932079895548186</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.218919445479023</v>
+        <v>0.2189194456335681</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>560.5151087608969</v>
+        <v>560.5151087608966</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>206.5</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.35950263639366</v>
+        <v>51.35950267679561</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.3772283094126</v>
+        <v>20.37722833651917</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.6932764350548071</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2624694073862628</v>
+        <v>-0.262469406974152</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>54.70325531137563</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.57255719085911</v>
+        <v>21.57255722333655</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.4062788842890289</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.3858920079068184</v>
+        <v>0.3858920083189496</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>541.3861736034136</v>
+        <v>541.2234279955438</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>56.6</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>62.00687006693687</v>
+        <v>56.88826731965816</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39.76788210143934</v>
+        <v>39.86515759927379</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>6.141559236203543</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0216950672160028</v>
+        <v>0.0411246298777926</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.73790875975013</v>
+        <v>53.73790874861631</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.21343953612984</v>
+        <v>31.21343953909047</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6821661129094115</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0042376395264384</v>
+        <v>-0.0042376395161352</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.25160073644322</v>
+        <v>49.25160066809106</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28.22482973259018</v>
+        <v>28.22482975890108</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.124858103722098</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0177253153801964</v>
+        <v>-0.0177253153492892</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.90329292417732</v>
+        <v>54.90329296354427</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.85910703950061</v>
+        <v>13.85910698199929</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.8783620724009343</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.722004197236819</v>
+        <v>0.7220041971543966</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>60.60189855266863</v>
+        <v>60.60189852930529</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.8090283025271</v>
+        <v>22.80902833913673</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.9252557792963276</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1824250914260921</v>
+        <v>0.1824250914054827</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.58571123169639</v>
+        <v>51.58571126071509</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>32.65780063079698</v>
+        <v>32.65780062106543</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.5389205543826759</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0470664700241442</v>
+        <v>-0.0470664700138391</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>521.6843918498165</v>
+        <v>521.6843918498166</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>49.6</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.38526401316417</v>
+        <v>48.38526398126483</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>34.41571793810463</v>
+        <v>34.41571799917731</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.3026979889460776</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1756035933440665</v>
+        <v>-0.1756035932822492</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.36772540895964</v>
+        <v>49.36772537039701</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>27.09979000889297</v>
+        <v>27.0997900198229</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.5201960900467223</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0043827808988232</v>
+        <v>-0.004382780867918</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>507.8444355676872</v>
+        <v>507.8444355676941</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>41.8</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>59.7045935678253</v>
+        <v>59.70459344154899</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.9554762704077</v>
+        <v>13.95547633483103</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.250867335614468</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1810026953540381</v>
+        <v>0.1810026955600994</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>503.8897072681284</v>
+        <v>503.8897072681285</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>122.5</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.19507216352279</v>
+        <v>52.19507220423252</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.65990353261184</v>
+        <v>12.65990355057724</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.6191517937938765</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.320985344975541</v>
+        <v>0.3209853448931216</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>501.6194299531392</v>
+        <v>501.6194299531393</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>116.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.64950869822994</v>
+        <v>51.649508785388</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.39842393918905</v>
+        <v>18.39842400647319</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.3794811507416541</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1113588162381193</v>
+        <v>0.1113588164441787</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.65573200731221</v>
+        <v>45.65573194439048</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>25.60104852354765</v>
+        <v>25.60104852329613</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.2889608618431269</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.3298249226896544</v>
+        <v>-0.3298249224320805</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>58.94982203768263</v>
+        <v>58.94982205557975</v>
       </c>
       <c r="I86" s="2" t="n">
         <v>18.09051244175178</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>2.263092228501216</v>
+        <v>2.263092228398176</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.19890145535545</v>
+        <v>49.19890133100287</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.98307787838852</v>
+        <v>27.98307793401825</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.3753585890398632</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0681684499623578</v>
+        <v>-0.06816844984902749</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.88149436443597</v>
+        <v>46.88149446316604</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.14945181664615</v>
+        <v>20.14945181842516</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.295609292796624</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1108843054387265</v>
+        <v>0.1108843054902433</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.81221921094188</v>
+        <v>53.8122191991387</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.98096661790582</v>
+        <v>17.98096650937949</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.4237673457920807</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1015492916748885</v>
+        <v>-0.1015492915440932</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>465.9103873813398</v>
+        <v>465.9103873813396</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>22.15</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54.45207047539888</v>
+        <v>54.45207036529564</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>29.76994783737446</v>
+        <v>29.76994827861668</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.168387659332808</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0067389438367672</v>
+        <v>-0.0067389437749514</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.38752713370236</v>
+        <v>53.38752713086369</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.01141671640656</v>
+        <v>11.01141672656926</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.758796288436487</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.341074765067795</v>
+        <v>0.3410747651090008</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>460.0072129166559</v>
+        <v>460.0072129166557</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>110.5</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.28140033787609</v>
+        <v>54.281400307232</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33.33672518999384</v>
+        <v>33.33672508379848</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.5031451363217708</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.5083043101415861</v>
+        <v>-0.5083043098737288</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>453.9479781898447</v>
+        <v>453.9479781898446</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>157</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.97505435013027</v>
+        <v>48.97505430610766</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.69767737416708</v>
+        <v>22.697677374783</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.6804432915929214</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1511271518700798</v>
+        <v>-0.1511271515609831</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>50.27947884873004</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.20616141891496</v>
+        <v>18.20616145951972</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.5486327017200211</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.63830618232691</v>
+        <v>47.63830617730443</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>22.70471723667156</v>
+        <v>22.70471723554974</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.2780363333781175</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6429381625963624</v>
+        <v>-0.6429381625778121</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>48.06737927961586</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.6205633109467</v>
+        <v>17.62056331263609</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.3390641895627444</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0114298492939641</v>
+        <v>0.011429849304268</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.08840640117938</v>
+        <v>52.08840656780885</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.78130064092308</v>
+        <v>11.78130063656162</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.070378057095349</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1695027486525568</v>
+        <v>-0.1695027484464995</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>48.68473597703824</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.91570447126345</v>
+        <v>14.91570461273282</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.7451925879109824</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0451123378361066</v>
+        <v>-0.045112337805202</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>48.17036737194626</v>
+        <v>48.1703672577143</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.51210448019348</v>
+        <v>11.51210452998784</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4366762645551951</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0491251944661215</v>
+        <v>0.0491251949812523</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>46.42495335805081</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.104543306448267</v>
+        <v>8.104543285710257</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.3776563173278241</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.5345072770962904</v>
+        <v>0.5345072771993116</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.82937864908997</v>
+        <v>51.8293786149213</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.16982552308462</v>
+        <v>12.16982552676058</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.6476695101355551</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1310540175941249</v>
+        <v>0.131054017635339</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.67681770385306</v>
+        <v>50.67681777857729</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>26.36655481137277</v>
+        <v>26.3665548128157</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.6099168589986705</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1268212015422719</v>
+        <v>0.1268212015834839</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.97388602170859</v>
+        <v>49.9738858666191</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.64623727803945</v>
+        <v>16.6462373293118</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.3593174657991511</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2595457452392737</v>
+        <v>0.2595457455689678</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>423.3505262535237</v>
+        <v>423.3505262535231</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>28.7</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.51502225487703</v>
+        <v>48.51502216475509</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>27.13784048492374</v>
+        <v>27.13784057496184</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.3587707070128833</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0228715623443372</v>
+        <v>0.0228715623649415</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>57.7315729951123</v>
+        <v>57.73157296552337</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>39.37055997151002</v>
+        <v>39.37055999853986</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.2783806282070347</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.7131639534482823</v>
+        <v>-0.7131639533040515</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>419.2082522500211</v>
+        <v>419.2082522500224</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>14.55</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>57.30937175489097</v>
+        <v>57.30937165579592</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>26.05147349756412</v>
+        <v>26.05147367241229</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.6291285620136361</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1706418058551027</v>
+        <v>0.1706418059890402</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>54.92261532032549</v>
+        <v>54.92261533321217</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>24.71221928716388</v>
+        <v>24.71221934747121</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7303268719256151</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0573684804597188</v>
+        <v>-0.0573684804700228</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>418.4677509516157</v>
+        <v>418.4677509516156</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>53.5</v>
@@ -6173,7 +6173,7 @@
         <v>51.27798183385112</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>30.60806253262957</v>
+        <v>30.60806253722804</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.5579357280046308</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0655211008840422</v>
+        <v>0.06552110125494651</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>25.8473095387144</v>
+        <v>25.8473094370114</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>23.20170646011513</v>
+        <v>23.20170648378391</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.004298944579714</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.8713996363103089</v>
+        <v>-0.8713996361145554</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.71445676075027</v>
+        <v>46.714456571095</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22.59778428002096</v>
+        <v>22.59778433124249</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.447164258059129</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0172574135499386</v>
+        <v>-0.0172574133644912</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.02846508235238</v>
+        <v>50.0284648587757</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.3745868565819</v>
+        <v>23.37458715478812</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5137929860233604</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0540217244501913</v>
+        <v>0.0540217245532221</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.33180246414615</v>
+        <v>51.33180255173658</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.91041555309456</v>
+        <v>16.91041557029057</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.6617970285298043</v>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.49045759241158</v>
+        <v>47.49045755073119</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.17048839018203</v>
+        <v>11.17048846874068</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.478352841420363</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.042871606414053</v>
+        <v>0.0428716064552637</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.16130049322625</v>
+        <v>42.16130053053652</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.36626462186889</v>
+        <v>20.3662646329971</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.346267025793898</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1683939437498295</v>
+        <v>-0.1683939436983196</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>54.18071854645888</v>
+        <v>54.18071860394543</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>42.66180060506735</v>
+        <v>42.66180058507521</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.985396946955504</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>1.460908972868529</v>
+        <v>1.460908972559454</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>35.33017294293859</v>
+        <v>35.33017269949924</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.57556026758535</v>
+        <v>20.5755603482364</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.8195590053092447</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0581904303111058</v>
+        <v>-0.0581904302389834</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.29786333710003</v>
+        <v>46.29786329106226</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.66646877948427</v>
+        <v>17.66646881634617</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.4434148942890911</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1535382110614119</v>
+        <v>0.1535382111541383</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.08063294447497</v>
+        <v>45.0806329203919</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.00430055511296</v>
+        <v>16.00430049633937</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.054679806868169</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.2252766594193209</v>
+        <v>0.225276659512061</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>381.7962757539569</v>
+        <v>381.7962757539568</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>34</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.67233973941142</v>
+        <v>50.6723394646711</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7.882847504328867</v>
+        <v>7.882847583875161</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>5.76803586874018</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.573586062773816</v>
+        <v>0.5735860626913908</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>379.5425614398257</v>
+        <v>379.5425614398258</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>12.85</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>58.89155717945496</v>
+        <v>58.89155703420016</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.57341765341546</v>
+        <v>19.57341760892318</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.920428471590874</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0160379289529161</v>
+        <v>0.0160379289632196</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>376.1165863815029</v>
+        <v>376.1165863814951</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>5.84</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>57.11017249195107</v>
+        <v>57.11017190365995</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.03521398516967</v>
+        <v>14.03521406941517</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.580507390686543</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0117176500771969</v>
+        <v>0.0117176501678637</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.87518725092141</v>
+        <v>45.87518721045134</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>26.63416884649561</v>
+        <v>26.63416883562056</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>1.287462745276025</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.2157265370775459</v>
+        <v>0.2157265371393635</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>368.5269097423981</v>
+        <v>368.5269097423962</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>14.35</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.85318375107787</v>
+        <v>46.85318373579547</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>24.94460501910953</v>
+        <v>24.94460506885646</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.6381629137303817</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0757074812457479</v>
+        <v>-0.07570748121483969</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>59.54895627736672</v>
+        <v>59.54895633336829</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.25480423616314</v>
+        <v>17.25480417542654</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.6617064745143563</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>47.08120464831508</v>
+        <v>47.0812046200564</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.78831501289716</v>
+        <v>17.78831505674852</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.5328576229744313</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0031906515222366</v>
+        <v>-0.0031906513573818</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>362.8347161560704</v>
+        <v>362.8347161560706</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>89.8</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>51.14349891511117</v>
+        <v>51.1434988342663</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.74667553396278</v>
+        <v>11.74667546960629</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.582835293248582</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0236759760347235</v>
+        <v>0.0236759762819908</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.38737824273832</v>
+        <v>44.38737822700613</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>10.55833093521616</v>
+        <v>10.55833092008607</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.8241658975993592</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.1230543231447265</v>
+        <v>0.123054323165333</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>59.00147193303981</v>
+        <v>59.00147192781249</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>24.02337483275518</v>
+        <v>24.02337481637796</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.8158927411499218</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.2309203638353976</v>
+        <v>0.2309203638457019</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>43.79565204219779</v>
+        <v>43.79565219370864</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6.775671568674396</v>
+        <v>6.775671548879134</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.5926859604038534</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.6601567588423518</v>
+        <v>0.6601567602847385</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.98292845481712</v>
+        <v>49.98292840362738</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>18.21300397079517</v>
+        <v>18.21300404315511</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.3029707186301835</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0136635060629367</v>
+        <v>0.0136635061453558</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46.47643373429103</v>
+        <v>46.47643377135237</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>23.534261688681</v>
+        <v>23.53426168205558</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.2260057699477646</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>38.63180068845332</v>
+        <v>38.63180075773519</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>19.5401220126883</v>
+        <v>19.54012202316894</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.5335407445864803</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1179219618929461</v>
+        <v>0.1179219620165821</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>347.1345179996736</v>
+        <v>347.1345179996734</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>11.45</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>51.95091787747056</v>
+        <v>51.95091787801213</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>8.036457185593516</v>
+        <v>8.036457188186887</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>1.260889693194731</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.07702248664655049</v>
+        <v>0.0770224865641273</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>345.5991223977944</v>
+        <v>345.5991223977943</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>21.95</v>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>56.91859460372653</v>
+        <v>56.918594669002</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>23.83867027518429</v>
+        <v>23.83867020259427</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.8594697219134093</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.2242095701655287</v>
+        <v>0.2242095701037113</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>52.42935139091559</v>
+        <v>52.4293513233108</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>30.81456032364536</v>
+        <v>30.8145603699585</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.1835439837347988</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.0229342816143187</v>
+        <v>0.0229342816658306</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>44.85298057027974</v>
+        <v>44.85298057822025</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>23.08189828071001</v>
+        <v>23.08189828816897</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.4015996922471406</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.208080220847405</v>
+        <v>0.2080802208680061</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>49.79393835552563</v>
+        <v>49.79393836153854</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>9.428521120298509</v>
+        <v>9.428521178312453</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.5243094935545702</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.0441972254481253</v>
+        <v>-0.0441972253038893</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>337.0085391037675</v>
+        <v>337.0085391037683</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>16.7</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>41.25643927421168</v>
+        <v>41.25643914202768</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>16.54126743018116</v>
+        <v>16.54126754666534</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>1.075102551451204</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.0066796512821746</v>
+        <v>-0.0066796512409638</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.57381639173779</v>
+        <v>45.57381638017899</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>17.37982892651469</v>
+        <v>17.37982889973134</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.2721357950214394</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-1.940798121570535</v>
+        <v>-1.940798121302645</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>47.50663165205417</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>7.996476970366555</v>
+        <v>7.996476972476405</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.3087616987234658</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.5862168273267838</v>
+        <v>0.5862168274504338</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>335.6758333273393</v>
+        <v>335.67583332734</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>14.05</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>49.12958495532696</v>
+        <v>49.12958477852224</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>18.84974837079224</v>
+        <v>18.84974857730242</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.3858598503153919</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.03090549094152</v>
+        <v>0.0309054910033366</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46.04534275319194</v>
+        <v>46.04534275783045</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.32337467168553</v>
+        <v>17.32337477170351</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.5365043057203819</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-53.60807011173248</v>
+        <v>-53.60807011286556</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>333.1681896029244</v>
+        <v>333.1681896029245</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>35.1</v>
@@ -8028,7 +8028,7 @@
         <v>45.13615146268742</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>16.02027051324852</v>
+        <v>16.02027049406712</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.1229158698705929</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.1026730175416565</v>
+        <v>0.102673017108934</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>43.32994608946719</v>
+        <v>43.32994609374284</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>15.64999284647921</v>
+        <v>15.649992895771</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.5807556794623164</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-5.642297907723779</v>
+        <v>-5.642297907826856</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>47.48955838204574</v>
+        <v>47.48955835170262</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>18.5311795135082</v>
+        <v>18.53117949621436</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.2983276393039684</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.0111527649197838</v>
+        <v>-0.0111527648991775</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>46.43879347864599</v>
+        <v>46.43879356684651</v>
       </c>
       <c r="I146" s="2" t="n">
         <v>12.31793859566326</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.0182312002412173</v>
+        <v>0.0182312002206126</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>39.9855799254952</v>
+        <v>39.9855799777564</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>34.18313940471126</v>
+        <v>34.18313938343775</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.6192139847116913</v>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>42.1197790527858</v>
+        <v>42.11977899068273</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>21.87212447052083</v>
+        <v>21.87212448425916</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.4200245246832342</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.2407776836145556</v>
+        <v>0.2407776837793986</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>310.9273160924817</v>
+        <v>310.9273160924815</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>167.5</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>45.70751077489438</v>
+        <v>45.70751059979891</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>12.71267553160699</v>
+        <v>12.71267563483869</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.8519733630675541</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.4410779062048816</v>
+        <v>-0.441077904659454</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>310.7084515435413</v>
+        <v>310.7084515435403</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>79</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>52.77468953189011</v>
+        <v>52.77468970436662</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>15.52418552748866</v>
+        <v>15.52418553572049</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>1.460674283264849</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.6152603184468115</v>
+        <v>0.6152603173134986</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>305.909651088082</v>
+        <v>305.9096510880813</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>22.3</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>50.0074943175717</v>
+        <v>50.00749391715368</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>18.67083881983958</v>
+        <v>18.67083892136684</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.4926732522737466</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.1800333049813787</v>
+        <v>0.180033305105013</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>300.4260525066554</v>
+        <v>300.4260525066556</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>8.710000000000001</v>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>42.35714294765609</v>
+        <v>42.35714312033581</v>
       </c>
       <c r="I152" s="2" t="n">
         <v>22.17384068872852</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.0188135981084552</v>
+        <v>0.0188135980569401</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>42.92988335297069</v>
+        <v>42.92988345768978</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>15.76283696345394</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.0146128462060336</v>
+        <v>-0.0146128462369426</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>42.49974213975087</v>
+        <v>42.49974209252884</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>21.87815293179382</v>
+        <v>21.87815293952445</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.4942439985358642</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.0184123358941639</v>
+        <v>-0.0184123358838611</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>295.4832750172131</v>
+        <v>295.4832750172137</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>270</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45.06314125797589</v>
+        <v>45.06314127752925</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>14.66170858871228</v>
+        <v>14.66170859448404</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.496030145088179</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.5821891722453421</v>
+        <v>0.582189172451403</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>45.26760312146568</v>
+        <v>45.26760308656569</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>15.8801310993294</v>
+        <v>15.8801310955963</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.3042759210368415</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.1211066962650683</v>
+        <v>0.1211066963268883</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>295.0159469538523</v>
+        <v>295.0159469538527</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>20.2</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>40.74145068311051</v>
+        <v>40.74145062283502</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>15.69733757893721</v>
+        <v>15.69733766260092</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.5740184986880712</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.0086461612228893</v>
+        <v>0.0086461612434939</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>48.7271469016414</v>
+        <v>48.72714686097271</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>28.7739602480958</v>
+        <v>28.77396024335008</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>1.808836261482356</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0246854214143882</v>
+        <v>0.0246854214246922</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>285.5963999673132</v>
+        <v>285.5963999673131</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>38.8</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>49.20575550305814</v>
+        <v>49.20575526039021</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>10.31812513792656</v>
+        <v>10.31812526424282</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.97932524966495</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.0182431016583829</v>
+        <v>-0.0182431014523301</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>43.33404085024337</v>
+        <v>43.33404095230412</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>10.82065860152653</v>
+        <v>10.82065856650007</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.8643340975524578</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.0480271422178357</v>
+        <v>-0.0480271422693503</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>43.64292931764186</v>
+        <v>43.64292932160161</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14.56223343340078</v>
+        <v>14.56223339709116</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.4797703254074707</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.364800564380946</v>
+        <v>0.3648005644324603</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>277.9807467383361</v>
+        <v>277.9807467383362</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>311</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>43.72484652487724</v>
+        <v>43.72484653944618</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>12.63302770145504</v>
+        <v>12.63302777673314</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.4284699608765883</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-1.942086313932548</v>
+        <v>-1.942086314138621</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>49.97179986410275</v>
+        <v>49.97179985603362</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>17.27350928453519</v>
+        <v>17.27350926039448</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.2386768137423381</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.0399617003288998</v>
+        <v>-0.0399617003062335</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>272.9031879208249</v>
+        <v>272.903187920825</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>15.8</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>41.03611118008397</v>
+        <v>41.03611114915553</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>20.09999893816644</v>
+        <v>20.0999988950579</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>1.222913540737807</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.07392005234564369</v>
+        <v>-0.0739200522638969</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>271.6782709060572</v>
+        <v>271.6782709060577</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>135</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46.19560326418512</v>
+        <v>46.19560302984972</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>17.19162582355158</v>
+        <v>17.19162570018274</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.972045504700522</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.5740223243855065</v>
+        <v>-0.5740223216037068</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>43.55850992283073</v>
+        <v>43.55850989791252</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>14.95365801601091</v>
+        <v>14.95365807536804</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.3143344608870071</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.0443577124285301</v>
+        <v>-0.0443577123976212</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>50.72258445313908</v>
+        <v>50.72258444433302</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>13.64931142857075</v>
+        <v>13.64931150607238</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>0.6259952648965221</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>2.970687145659483</v>
+        <v>2.970687147575813</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>269.0142934329536</v>
+        <v>269.0142934329537</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>46.67619534707182</v>
+        <v>46.67619535120613</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>6.453041656292206</v>
+        <v>6.453041605432626</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.2459001766626813</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.0787108518744228</v>
+        <v>-0.07871085207017769</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>267.7643638055043</v>
+        <v>267.7643638055042</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>176.5</v>
@@ -9406,7 +9406,7 @@
         <v>39.85459427699051</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>7.734047185778231</v>
+        <v>7.734047268038883</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.8132687948270095</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.0757201861841857</v>
+        <v>-0.07572018608115549</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>44.78916472860934</v>
+        <v>44.78916457879095</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>13.36782971869872</v>
+        <v>13.36782961912087</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.06464680011044061</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.0489651672701745</v>
+        <v>-0.0489651670435052</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>54.38168326325388</v>
+        <v>54.38168335236679</v>
       </c>
       <c r="I171" s="2" t="n">
         <v>14.49687447697789</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.1307119084685846</v>
+        <v>0.1307119084582813</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>47.39154673994332</v>
+        <v>47.39154670590759</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>17.00134592574634</v>
+        <v>17.00134590078915</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>1.995181829132206</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.1388937333857656</v>
+        <v>-0.1388937330766992</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>261.1915923965753</v>
+        <v>261.1915923965755</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>52.4</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>48.26072488213692</v>
+        <v>48.26072482753818</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>24.66940584683242</v>
+        <v>24.66940591497459</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.6529792332296629</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.3691319575018397</v>
+        <v>0.3691319576666787</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>255.3848237112073</v>
+        <v>255.3848237112072</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>17.8</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>51.08349064557819</v>
+        <v>51.08349067309661</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>18.15042997007818</v>
+        <v>18.15042997327016</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.5267471855237816</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.0652299107784233</v>
+        <v>-0.0652299107475138</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>43.13583134514838</v>
+        <v>43.13583114864292</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>36.18594859647976</v>
+        <v>36.18594860672797</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.4970363771925189</v>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>43.5698329510488</v>
+        <v>43.56983295966588</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>25.82065214412445</v>
+        <v>25.82065216537687</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.5810851980984568</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.0627217036379365</v>
+        <v>0.0627217036997563</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>40.89242013154277</v>
+        <v>40.89242074256417</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>25.8625810465589</v>
+        <v>25.86258110765038</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.5278341508844057</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.0901531139897131</v>
+        <v>0.0901531141236476</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>35.86504762454824</v>
+        <v>35.86504768141444</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>35.56214034173716</v>
+        <v>35.5621403386705</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>1.046886564675346</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.0251501072169428</v>
+        <v>0.0251501072066392</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>52.59721421470664</v>
+        <v>52.59721389319981</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>13.44019581472999</v>
+        <v>13.44019579660441</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.7013086436674785</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.0418599962092272</v>
+        <v>0.041859996283408</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>42.46186670057893</v>
+        <v>42.46186654114118</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>9.438909909963879</v>
+        <v>9.438909905660983</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.3178817055022465</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>0.308367907271859</v>
+        <v>0.3083679077869976</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>51.61016760880933</v>
+        <v>51.61016759845739</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>5.984752437925387</v>
+        <v>5.98475244346644</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>5.445339721254356</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.1734335344481401</v>
+        <v>0.173433534489352</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>54.2986377656468</v>
+        <v>54.29863770438976</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>13.69317586336206</v>
+        <v>13.6931759231227</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.5481983745526132</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.0859768595705083</v>
+        <v>0.0859768596735377</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10120,21 +10120,21 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>2459</v>
+        <v>3071</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>協禧</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>238.6108977332696</v>
+        <v>236.4509140939904</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>65.2</v>
+        <v>23</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10145,13 +10145,13 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>39.13604785927883</v>
+        <v>35.76647313418464</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>17.76102632733234</v>
+        <v>28.9586661898901</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>1.245047455722776</v>
+        <v>0.908478849668597</v>
       </c>
       <c r="K183" s="2" t="n">
         <v>0</v>
@@ -10163,31 +10163,31 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.09554800484215779</v>
+        <v>0.0120880190974727</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>3071</v>
+        <v>2630</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>協禧</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>236.4509140939896</v>
+        <v>234.6644236694675</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>23</v>
+        <v>46.3</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10198,16 +10198,16 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>35.76647322856583</v>
+        <v>37.4191399593828</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>28.95866620431842</v>
+        <v>12.74610741490159</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.908478849668597</v>
+        <v>0.4076717466641136</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L184" s="2" t="n">
         <v>0</v>
@@ -10216,51 +10216,51 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.012088019004746</v>
+        <v>-0.1935094954124121</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>2630</v>
+        <v>2601</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>234.6644236694675</v>
+        <v>232.8699039137718</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>46.3</v>
+        <v>5.91</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G185" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>37.41913998850432</v>
+        <v>32.07840552986299</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>12.74610747171266</v>
+        <v>24.78126983109538</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.4076717466641136</v>
+        <v>1.073534091798287</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L185" s="2" t="n">
         <v>0</v>
@@ -10269,48 +10269,48 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.1935094962160418</v>
+        <v>-0.1041450107062202</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>2601</v>
+        <v>3043</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>益航</t>
+          <t>科風</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>232.8699039137719</v>
+        <v>226.7554445610611</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>5.91</v>
+        <v>20.6</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G186" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>32.07840557249774</v>
+        <v>47.71145058913496</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>24.78126981991767</v>
+        <v>9.305390168773208</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>1.073534091798287</v>
+        <v>0.4769543286900412</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>0</v>
@@ -10322,31 +10322,31 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.1041450107230444</v>
+        <v>0.0215408856137605</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>3043</v>
+        <v>3050</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>科風</t>
+          <t>鈺德</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>226.7554445610611</v>
+        <v>218.984969863611</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>20.6</v>
+        <v>11.5</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,16 +10357,16 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>47.71145049444481</v>
+        <v>51.48917584088885</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>9.305390151902223</v>
+        <v>19.17109230725874</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.4769543286900412</v>
+        <v>0.9910641144518282</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L187" s="2" t="n">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.0215408855828482</v>
+        <v>0.0399803815634192</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10385,21 +10385,21 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>3050</v>
+        <v>2762</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>鈺德</t>
+          <t>世界健身-KY</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>218.9849698636111</v>
+        <v>217.6749617750666</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>11.5</v>
+        <v>79</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>51.48917592251704</v>
+        <v>35.8277267415755</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>19.17109221253254</v>
+        <v>12.54106871543868</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.9910641144518282</v>
+        <v>0.9010942548818665</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188" s="2" t="n">
         <v>0</v>
@@ -10428,31 +10428,31 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>0.0399803815119055</v>
+        <v>-0.0363592680672817</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>2762</v>
+        <v>3018</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>世界健身-KY</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>217.6749617750667</v>
+        <v>212.0619685497002</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>35.82772670019038</v>
+        <v>48.83231427448287</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>12.54106860323498</v>
+        <v>7.9655624358996</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.9010942548818665</v>
+        <v>0.7080780095120344</v>
       </c>
       <c r="K189" s="2" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0363592680054627</v>
+        <v>0.115007951313549</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10491,21 +10491,21 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>3018</v>
+        <v>2537</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>212.0619685497002</v>
+        <v>210.6450921872513</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>48.83231444570642</v>
+        <v>52.2801062722442</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>7.965562239434558</v>
+        <v>19.36610584293786</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.7080780095120344</v>
+        <v>0.2546733899508159</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>0</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.1150079510868856</v>
+        <v>-0.0095376841753292</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>2537</v>
+        <v>2706</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>聯上發</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>210.6450921872502</v>
+        <v>207.9549031970724</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,13 +10569,13 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>52.2801062983641</v>
+        <v>34.86612435542446</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>19.36610587317592</v>
+        <v>21.39735169232606</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.2546733899508159</v>
+        <v>0.3128241851823178</v>
       </c>
       <c r="K191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.009537684185631499</v>
+        <v>-0.010073319724306</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>2706</v>
+        <v>2485</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>第一店</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>207.9549031970724</v>
+        <v>207.8116985399516</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>12.1</v>
+        <v>39.15</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,13 +10622,13 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>34.86612435542446</v>
+        <v>43.47314717154531</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>21.39735169232606</v>
+        <v>10.56445134033725</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.3128241851823178</v>
+        <v>0.4488384159978575</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.0100733197140043</v>
+        <v>0.0987722358148834</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>2485</v>
+        <v>2539</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>207.8116985399516</v>
+        <v>207.2838471656833</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>39.15</v>
+        <v>34.45</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>43.47314717154531</v>
+        <v>39.64479947649146</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>10.56445136555818</v>
+        <v>22.28291884341842</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.4488384159978575</v>
+        <v>1.295496853376137</v>
       </c>
       <c r="K193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.0987722357736731</v>
+        <v>0.1973509142153646</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>2539</v>
+        <v>2731</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>207.2838471656833</v>
+        <v>204.0994422181576</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>34.45</v>
+        <v>144</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>39.64479955754189</v>
+        <v>51.94442401826269</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>22.28291869984292</v>
+        <v>12.35032184695256</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>1.295496853376137</v>
+        <v>0.7223821115199547</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.1973509140299136</v>
+        <v>0.3583649635878673</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>2731</v>
+        <v>2913</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>204.0994422181571</v>
+        <v>203.499420338118</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>144</v>
+        <v>11.05</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>51.94442396043193</v>
+        <v>49.73472656838773</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>12.35032165279449</v>
+        <v>16.51563521622405</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.7223821115199547</v>
+        <v>0.718347127290573</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>0.3583649629696843</v>
+        <v>0.008613769668921099</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>2913</v>
+        <v>2812</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>農林</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>203.499420338118</v>
+        <v>202.131456511834</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>11.05</v>
+        <v>19</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,13 +10834,13 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>49.73472640399152</v>
+        <v>42.83119799910645</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>16.51563516846662</v>
+        <v>14.30686861704171</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.718347127290573</v>
+        <v>0.7132675923781538</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>0</v>
@@ -10852,31 +10852,31 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.008613769679224</v>
+        <v>-0.0144178091835507</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>2812</v>
+        <v>2705</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>202.1314565118343</v>
+        <v>201.1995482303353</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>19</v>
+        <v>15.15</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,13 +10887,13 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>42.83119804311929</v>
+        <v>34.26531010547117</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>14.30686841516984</v>
+        <v>31.64489943374472</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.7132675923781538</v>
+        <v>0.5312559599216675</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.0144178092762771</v>
+        <v>-0.0185792152421115</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>2705</v>
+        <v>2701</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>萬企</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>201.1995482303353</v>
+        <v>199.3249747992888</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>15.15</v>
+        <v>10.25</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>34.26531020059764</v>
+        <v>35.48545801213805</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>31.64489942130568</v>
+        <v>17.91223243823407</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.5312559599216675</v>
+        <v>1.81821377534255</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -10958,31 +10958,31 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.0185792152627157</v>
+        <v>-0.0037310734506911</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>2701</v>
+        <v>2832</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>萬企</t>
+          <t>台產</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>199.3249747992888</v>
+        <v>197.3554857080668</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>10.25</v>
+        <v>57.5</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,13 +10993,13 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>35.48545812116821</v>
+        <v>44.13952005150704</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>17.91223243823407</v>
+        <v>15.21086694901195</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>1.81821377534255</v>
+        <v>0.3594038178346627</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
@@ -11011,31 +11011,31 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0037310734609928</v>
+        <v>-0.0321944987215593</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>2832</v>
+        <v>2910</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>台產</t>
+          <t>統領</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>197.3554857080667</v>
+        <v>195.07299698767</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>57.5</v>
+        <v>23.55</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,13 +11046,13 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>44.13952003074752</v>
+        <v>47.10346881008327</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>15.21086698315248</v>
+        <v>15.09069111689901</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.3594038178346627</v>
+        <v>0.2340763027948071</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>0</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0321944987921872</v>
+        <v>0.0176083630757132</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11074,21 +11074,21 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>2910</v>
+        <v>3046</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>統領</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>195.07299698767</v>
+        <v>194.7650261667224</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>23.55</v>
+        <v>53.8</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>47.10346883415108</v>
+        <v>44.94194026293313</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>15.09069109745988</v>
+        <v>12.28474543588354</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.2340763027948071</v>
+        <v>0.3109870550503462</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.0176083630757132</v>
+        <v>0.09846700845423451</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>3046</v>
+        <v>2712</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>遠雄來</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>194.7650261667224</v>
+        <v>193.5538170221248</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>53.8</v>
+        <v>13.35</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>44.941940139458</v>
+        <v>44.11361130971607</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>12.28474543588354</v>
+        <v>7.490084205232517</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.3109870550503462</v>
+        <v>0.2553817022124776</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,31 +11170,31 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.09846700845423451</v>
+        <v>-0.1008334848882574</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>2712</v>
+        <v>2616</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>遠雄來</t>
+          <t>山隆</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>193.5538170221248</v>
+        <v>192.7088497608091</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>13.35</v>
+        <v>13.2</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,13 +11205,13 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>44.11361131766094</v>
+        <v>37.05388110704727</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>7.490084279523421</v>
+        <v>11.34587208495236</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.2553817022124776</v>
+        <v>0.9931541841217942</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
@@ -11223,31 +11223,31 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.1008334848985614</v>
+        <v>-0.006453787275981</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>2616</v>
+        <v>2904</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>山隆</t>
+          <t>匯僑</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>192.7088497608091</v>
+        <v>187.9970275400316</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>13.2</v>
+        <v>12.55</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,13 +11258,13 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>37.0538811500088</v>
+        <v>36.80541839176845</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>11.34587208495236</v>
+        <v>26.15819044067358</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.9931541841217942</v>
+        <v>0.6583939932366596</v>
       </c>
       <c r="K204" s="2" t="n">
         <v>0</v>
@@ -11276,31 +11276,31 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.006453787275981</v>
+        <v>0.0173775427869626</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>2904</v>
+        <v>2614</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>匯僑</t>
+          <t>東森</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>187.9970275400316</v>
+        <v>181.6486911239652</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>12.55</v>
+        <v>18.25</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,13 +11311,13 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>36.80541842566177</v>
+        <v>53.5386248579811</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>26.15819039818314</v>
+        <v>13.9813344642074</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.6583939932366596</v>
+        <v>0.5570884225910847</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>0</v>
@@ -11329,31 +11329,31 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.0173775427869626</v>
+        <v>0.0364684957832615</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>2614</v>
+        <v>3078</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>東森</t>
+          <t>僑威</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>181.6486911239658</v>
+        <v>179.6961425127746</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>18.25</v>
+        <v>45.45</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,16 +11364,16 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>53.53862487842444</v>
+        <v>39.79735722220075</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>13.98133445380212</v>
+        <v>37.5660759340992</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.5570884225910847</v>
+        <v>0.2992393094662611</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>0</v>
@@ -11382,31 +11382,31 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>0.0364684957626579</v>
+        <v>0.3176299904228228</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>3078</v>
+        <v>2459</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>僑威</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>179.6961425127746</v>
+        <v>178.6108977332696</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>45.45</v>
+        <v>65.2</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,16 +11417,16 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>39.79735694247898</v>
+        <v>39.13604749928031</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>37.56607599041978</v>
+        <v>17.76102630622755</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.2992393094662611</v>
+        <v>1.245047455722776</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>0</v>
@@ -11435,11 +11435,11 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>0.3176299906700932</v>
+        <v>-0.09554800459488171</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>176.3234985183479</v>
+        <v>176.3234985183478</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>21.1</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>32.5397098371578</v>
+        <v>32.53970974171489</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>17.28163095364844</v>
+        <v>17.28163096412397</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.802913568084109</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.07342572872575349</v>
+        <v>-0.0734257286742391</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>43.88657110871775</v>
+        <v>43.88657111640747</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>13.81865788680341</v>
+        <v>13.81865788620261</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.3826614728232183</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0327079473719064</v>
+        <v>0.0327079473925121</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>29.72809220310336</v>
+        <v>29.72809228830972</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>10.56661076230796</v>
+        <v>10.5666107256688</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.5252776297071031</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.0050062206503012</v>
+        <v>-0.0050062206853309</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>166.0575727898998</v>
+        <v>166.0575727899005</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>20.3</v>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>31.78564343480288</v>
+        <v>31.78564330734447</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>13.68267756400023</v>
+        <v>13.68267753914041</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.2019509158175141</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.1767974480465546</v>
+        <v>-0.1767974479641316</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>50.93699124065921</v>
+        <v>50.93699110253439</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>18.58774929216165</v>
+        <v>18.5877492657956</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.4308406086998798</v>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>157.8086057266997</v>
+        <v>157.8086057266999</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>19.55</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>42.0912723812468</v>
+        <v>42.09127233424995</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>14.63116919452008</v>
+        <v>14.63116927071275</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.4295264711535195</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.0276204602280673</v>
+        <v>0.0276204602795814</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>42.92552378413596</v>
+        <v>42.92552372336893</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>18.99979331496127</v>
+        <v>18.99979331323352</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.3518089708795248</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.0068861433629184</v>
+        <v>0.0068861433835256</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>51.40905224601266</v>
+        <v>51.40905223156475</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>11.47552047473076</v>
+        <v>11.47552052240313</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>1.246427831007443</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.5371268921504719</v>
+        <v>0.5371268922638065</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>50.13127786983037</v>
+        <v>50.13127799260133</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>15.12158398898943</v>
+        <v>15.12158397823989</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.3145204661705998</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.2518789860022919</v>
+        <v>0.2518789856932057</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>129.8060301276402</v>
+        <v>129.8060301276375</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>34.85</v>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>49.43564346635288</v>
+        <v>49.43564338622819</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>10.02768877277427</v>
+        <v>10.02768879140807</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.3325436223774075</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.0828977126376963</v>
+        <v>0.0828977127819349</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>45.59315514613103</v>
+        <v>45.59315516888431</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>16.6420785924543</v>
+        <v>16.64207866384152</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.8075433008303744</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.0163701600310878</v>
+        <v>0.0163701600413878</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>125.6570182468047</v>
+        <v>125.6570182468045</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>24</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>40.10747330770218</v>
+        <v>40.10747332875209</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>11.68341645544646</v>
+        <v>11.68341648401103</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.3179352463744321</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.017815844066558</v>
+        <v>0.0178158440356533</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>46.72162655551215</v>
+        <v>46.72162657407137</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>17.00697311366238</v>
+        <v>17.00697307755958</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.738807171614679</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.0021399113785521</v>
+        <v>-0.0021399113579464</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>117.1414522817726</v>
+        <v>117.1414522817723</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>30.9</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>45.18935730298345</v>
+        <v>45.18935731417918</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>12.79619403719512</v>
+        <v>12.79619415464154</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>1.18926602042421</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>-0.009704878176015201</v>
+        <v>-0.009704878052379099</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>113.2015686813886</v>
+        <v>113.2015686813885</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>21.1</v>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>41.0526161446267</v>
+        <v>41.05261633072645</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>7.967565083953181</v>
+        <v>7.967565193844907</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>1.080762414150299</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.0043255748242742</v>
+        <v>-0.004325574896394</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>48.14454296739727</v>
+        <v>48.14454273760116</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>15.65328736089258</v>
+        <v>15.65328752033381</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.2920002645023277</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>-0.0320563196049252</v>
+        <v>-0.0320563193061418</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq3_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq3_2026-09-24.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.35916913022429</v>
+        <v>67.35916904423975</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.97984075438159</v>
+        <v>31.97984080090087</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.673234644587856</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.447133789504097</v>
+        <v>1.447133789570857</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>84.20044562378624</v>
+        <v>84.20044561478478</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.24541071178341</v>
+        <v>31.24541061817106</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.193580447083624</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.170439484051052</v>
+        <v>5.170439484262467</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.87252199904209</v>
+        <v>63.87252200705429</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.27645977317179</v>
+        <v>12.27645980554614</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3.118061260819318</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.164259126577903</v>
+        <v>2.164259126177338</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.38368042998331</v>
+        <v>68.38368042610527</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.18342025045289</v>
+        <v>18.183420243439</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.7299822735647015</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>21.70405307708353</v>
+        <v>21.70405307719479</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1050.256072845671</v>
+        <v>1050.256072845672</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>57.8</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>77.37795194013464</v>
+        <v>77.37795194478123</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>40.97035183197509</v>
+        <v>40.97035181065333</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.9879942208468172</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.5387213948067895</v>
+        <v>0.5387213948290484</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>73.79047159679217</v>
+        <v>73.79047158065764</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.22731104692292</v>
+        <v>30.22731104333497</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.8876246206235756</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>63.78141624723742</v>
+        <v>63.78141624946323</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.47202487315005</v>
+        <v>59.47202487210125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.38837741342502</v>
+        <v>20.38837749720306</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.25730677294057</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.769731796254845</v>
+        <v>2.769731796432843</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>973.7590327297444</v>
+        <v>973.7590327297446</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>15.45</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>73.32187868809459</v>
+        <v>73.32187860924198</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>54.04532288050641</v>
+        <v>54.04532288582527</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>4.967729596012565</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0766607972022554</v>
+        <v>0.0766607972356375</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>69.61414719240109</v>
+        <v>69.61414711085453</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.64512125759297</v>
+        <v>19.6451211605728</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.212851387665661</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.739771419493755</v>
+        <v>3.739771420050118</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>73.96907369390064</v>
+        <v>73.96907368045299</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.00189199980414</v>
+        <v>26.00189185492298</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3.500817928999779</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.6423718146587302</v>
+        <v>0.6423718147477459</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.37860023843704</v>
+        <v>60.37860025131144</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.93591435853957</v>
+        <v>18.93591438468679</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2.160979960883878</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0749558789571195</v>
+        <v>0.0749558790016199</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.89602078156517</v>
+        <v>63.89602077298118</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.17909778673937</v>
+        <v>21.17909774831083</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.6718090943420125</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.479871943040244</v>
+        <v>2.479871943173819</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>67.89175037465733</v>
+        <v>67.89175037102618</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.55489951616129</v>
+        <v>41.55489942229397</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.092277299122219</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.119965501195986</v>
+        <v>1.119965501251614</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>877.041950028925</v>
+        <v>877.0419500289252</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>45.15</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>66.2881730917688</v>
+        <v>66.28817310375044</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45.56647560519136</v>
+        <v>45.5664755835848</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.3668933933738023</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0368222159991882</v>
+        <v>0.0368222160436975</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.30918122553471</v>
+        <v>57.30918123223005</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.87256554378452</v>
+        <v>34.8725654530171</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.2796491076966693</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.92637705377061</v>
+        <v>64.92637706735448</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>54.36731955234778</v>
+        <v>54.36731955840374</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.3660903341828601</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1682353413461066</v>
+        <v>-0.1682353413349862</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.13343433705232</v>
+        <v>59.13343437378892</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46.68728141995782</v>
+        <v>46.68728143909281</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.3340836202469773</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.0689245957560817</v>
+        <v>-0.0689245957783384</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>66.40067753823446</v>
+        <v>66.40067753369988</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46.53928448122154</v>
+        <v>46.53928461844507</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.3212201754351927</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0122485876527753</v>
+        <v>0.0122485877195368</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>77.88064052877513</v>
+        <v>77.88064054859746</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>40.25373284014363</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3916320231764109</v>
+        <v>0.3916320231652829</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.40481763350751</v>
+        <v>62.40481762678413</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.1549621678079</v>
+        <v>17.15496208984618</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7376549092976042</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-4.686429046003269</v>
+        <v>-4.686429036434021</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>65.60701070080064</v>
+        <v>65.60701067576284</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>23.55212400341363</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.336923079532603</v>
+        <v>5.336923079755127</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.02065774532169</v>
+        <v>57.02065774330686</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.637573600257724</v>
+        <v>9.637573620403408</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>4.776461597248758</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.908459310225171</v>
+        <v>2.908459309913613</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.80246135917142</v>
+        <v>58.80246136973006</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>34.13382584366163</v>
+        <v>34.13382586719253</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.5447156714186273</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3162972839449085</v>
+        <v>0.316297284278721</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>795.3674628519854</v>
+        <v>795.3674628519852</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>174.5</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.29035184445677</v>
+        <v>63.29035182846431</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.72287881601898</v>
+        <v>26.72287874414357</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.8336037653263562</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.748109083437771</v>
+        <v>1.748109083660331</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>68.56974881166477</v>
+        <v>68.56974881986793</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37.01260481840499</v>
+        <v>37.01260484678122</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.4242626749866391</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1430065580391487</v>
+        <v>0.1430065580502785</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.63548612623081</v>
+        <v>56.63548616060312</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.70530163230243</v>
+        <v>37.70530159241387</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.5745505998409098</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.4714607840556386</v>
+        <v>-0.4714607841669043</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>781.8559992684578</v>
+        <v>781.8559992684575</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>37.3</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.02429238980737</v>
+        <v>56.0242934948814</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.53234226830413</v>
+        <v>26.53234249023686</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.5857464506086772</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0053402907334084</v>
+        <v>0.0053402889308056</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.63200395242674</v>
+        <v>65.63200402949775</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>44.03839051999199</v>
+        <v>44.03839046768381</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.6078466135900267</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0200817772645875</v>
+        <v>0.0200817771533179</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.03787099788722</v>
+        <v>54.03787099520947</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.23262634001929</v>
+        <v>21.23262630024963</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.8266157303687118</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5900449166993122</v>
+        <v>-0.5900449167215789</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.68173830645227</v>
+        <v>59.68173848604049</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>39.04824346071764</v>
+        <v>39.04824369992065</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>3.448151378147453</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0340294751758051</v>
+        <v>-0.0340294751099653</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.7084390896032</v>
+        <v>65.70843910373418</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.7483364292437</v>
+        <v>30.74833642026831</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.4769846008235309</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.28471339749531</v>
+        <v>54.28471338535627</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.46045149857574</v>
+        <v>29.46045154989378</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.2751369455789065</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1408774067926554</v>
+        <v>-0.1408774067704017</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>715.4061651345168</v>
+        <v>715.4061651345166</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>53.7</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>66.47537497301997</v>
+        <v>66.47537470119616</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.43737757719676</v>
+        <v>34.43737782058288</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6353217541953575</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1192522031800613</v>
+        <v>-0.1192522029858396</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.05103662537523</v>
+        <v>49.05103666481354</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6.746885923488451</v>
+        <v>6.74688592785708</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.130968915394447</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0284632964550583</v>
+        <v>0.0284632964661776</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.9065551669526</v>
+        <v>57.90655517441348</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41.29653187313866</v>
+        <v>41.29653183989086</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.4982045516824597</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.4682505718986176</v>
+        <v>-0.4682505719208758</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.69598003608613</v>
+        <v>58.69598010396992</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>42.80766436637772</v>
+        <v>42.80766436401933</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.005977935548722</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2585207001461249</v>
+        <v>0.258520700190632</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>694.5165867025813</v>
+        <v>694.5165867025797</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>39.05</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>56.12825463730253</v>
+        <v>56.12825462250493</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.60526606342553</v>
+        <v>20.60526605553344</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.6236515273155553</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3191484052967197</v>
+        <v>0.3191484053078449</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>689.1997426908691</v>
+        <v>689.1997426908692</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>218.5</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.76993626128969</v>
+        <v>46.76993625323456</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.32536384260998</v>
+        <v>18.32536392348801</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.7514507125224493</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.411618711826481</v>
+        <v>2.411618711960029</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.09556874383137</v>
+        <v>53.09556876541751</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.92702859094246</v>
+        <v>24.92702859675166</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.5109684579988553</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.001115253086128</v>
+        <v>0.0011152530749898</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>72.90923582726089</v>
+        <v>72.90923582087284</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45.06807125701642</v>
+        <v>45.068071213664</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.430545199742318</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>5.247779446925852</v>
+        <v>5.247779447081653</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>677.0225248290176</v>
+        <v>677.0225248290177</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>47.95</v>
@@ -2781,7 +2781,7 @@
         <v>64.81979586832728</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.15358691752214</v>
+        <v>20.15358694767053</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.7606312418924172</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5870559049621462</v>
+        <v>0.5870559049843939</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>674.8363581429958</v>
+        <v>674.8363581429959</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>140.5</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>64.36623523882781</v>
+        <v>64.36623517942175</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.15052493678222</v>
+        <v>25.15052506249009</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.738508582357415</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.298319388673268</v>
+        <v>1.298319389229629</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.13189454941945</v>
+        <v>56.13189451997651</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>35.29499653393963</v>
+        <v>35.29499654579908</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.3263114045187097</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.8946366111390676</v>
+        <v>-0.8946366110945583</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>60.91303303407285</v>
+        <v>60.91303304587124</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.9529880684167</v>
+        <v>19.95298810962252</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.5487289514262077</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0420972841190074</v>
+        <v>-0.0420972842302775</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>58.51130385479171</v>
+        <v>58.51130387829137</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>41.73758584169226</v>
+        <v>41.7375857871774</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.4327569967903438</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.008334378346628099</v>
+        <v>-0.0083343783510795</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>61.47641033516549</v>
+        <v>61.47641036437248</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>40.67867143361326</v>
+        <v>40.67867141565173</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.5580046851103763</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1970774192776709</v>
+        <v>-0.1970774192999262</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>54.53426938901874</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12.56908560376613</v>
+        <v>12.56908567290349</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>2.556955301050489</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2205986750806834</v>
+        <v>0.2205986749693986</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>62.70492622189055</v>
+        <v>62.70492623730991</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.5726266523497</v>
+        <v>29.57262663935941</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.877043670878189</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1833856631456493</v>
+        <v>0.1833856631011379</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.68288336067212</v>
+        <v>54.68288332436871</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>29.74872005201946</v>
+        <v>29.74872011492989</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.173434029982644</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1275764611958327</v>
+        <v>0.1275764613293493</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>61.74059552302887</v>
+        <v>61.74059554228992</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>49.21548351243336</v>
+        <v>49.21548350248306</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.5726301357151715</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0849281708396787</v>
+        <v>-0.0849281708285456</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.65241739512869</v>
+        <v>54.65241732494037</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10.76501941195043</v>
+        <v>10.76501938827591</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.7168588642303524</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.91925493622543</v>
+        <v>0.9192549365592432</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.67693326464157</v>
+        <v>50.67693317072307</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26.39516869616953</v>
+        <v>26.3951687214821</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.114428752024756</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.4484933539638</v>
+        <v>52.44849334058213</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.96932515640457</v>
+        <v>12.96932519419178</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.5245690437060039</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.6625484989455073</v>
+        <v>0.6625484993238095</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>59.08004656023282</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>43.93934301878588</v>
+        <v>43.9393430359584</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3375388084709775</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2367731122542706</v>
+        <v>-0.2367731122431402</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.65613517605325</v>
+        <v>54.65613518501956</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>32.74819240474837</v>
+        <v>32.74819236840205</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.5897709705302236</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.06461666740951209</v>
+        <v>-0.0646166674206364</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>603.7128019628905</v>
+        <v>603.7128019628906</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>38.95</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>65.74730363400623</v>
+        <v>65.74730363723992</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>51.74840057359858</v>
+        <v>51.74840059655314</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4187237161791118</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0389592488933014</v>
+        <v>-0.0389592488821795</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>58.40839283050396</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>50.11875966251016</v>
+        <v>50.11875967928869</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.3825660459611733</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.06865857773819251</v>
+        <v>-0.0686585777048145</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>597.0254310918561</v>
+        <v>597.0254310918563</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>150</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>57.21175702700567</v>
+        <v>57.21175703594913</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>35.66884884514631</v>
+        <v>35.66884883937119</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.4813969357462679</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.4381822730116</v>
+        <v>53.43818247845776</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38.26028241630205</v>
+        <v>38.26028286424517</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.1642424133129711</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.001026604457602</v>
+        <v>0.0010266042795685</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>54.23745266667906</v>
+        <v>54.23745275926357</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.85420866066544</v>
+        <v>29.85420864222666</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.6626142553186907</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0458551234189655</v>
+        <v>-0.0458551234412187</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>65.39030737444013</v>
+        <v>65.39030740791134</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.53692513633971</v>
+        <v>18.53692518042164</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.8186746019670171</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1812650815015961</v>
+        <v>0.1812650815238495</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.04483873514064</v>
+        <v>51.0448387166286</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.11064850021859</v>
+        <v>21.11064857347218</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5033120834426517</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-126.9959291948374</v>
+        <v>-126.9959291859357</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.48768478134322</v>
+        <v>53.4876848607556</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>37.4408071718121</v>
+        <v>37.44080707786487</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.3390684969860393</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.4420175373160653</v>
+        <v>-0.4420175374384572</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.07874674727562</v>
+        <v>54.07874697373823</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.47956845688448</v>
+        <v>21.47956901499107</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4695103352807301</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0522716895780821</v>
+        <v>-0.0522716907575531</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>35.3388870173778</v>
+        <v>35.33888689924531</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.68602299646167</v>
+        <v>23.68602307056643</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1.488147275173699</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0554415467327595</v>
+        <v>-0.0554415465102193</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4356850996232211</v>
+        <v>0.4356850996454788</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.93238457347596</v>
+        <v>49.93238456512401</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.74391895480696</v>
+        <v>21.74391890880162</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.3859460029097875</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-3.316216138905379</v>
+        <v>-3.316216138660576</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.24153667533946</v>
+        <v>53.24153660249301</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.32630905884131</v>
+        <v>21.32630909656192</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.7932079895548186</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2189194456335681</v>
+        <v>0.2189194457225828</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>560.5151087608966</v>
+        <v>560.5151087608965</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>206.5</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.35950267679561</v>
+        <v>51.35950246807477</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.37722833651917</v>
+        <v>20.37722846252785</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.6932764350548071</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.262469406974152</v>
+        <v>-0.2624694061952537</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>54.70325531137563</v>
+        <v>54.70325532892889</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.57255722333655</v>
+        <v>21.57255736862977</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.4062788842890289</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.3858920083189496</v>
+        <v>0.3858920087640261</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>541.2234279955438</v>
+        <v>541.3768406551036</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>56.6</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>56.88826731965816</v>
+        <v>58.39727960191266</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39.86515759927379</v>
+        <v>35.33531240829412</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>6.141559236203543</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0411246298777926</v>
+        <v>0.0498600728527141</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.73790874861631</v>
+        <v>53.73790873468844</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.21343953909047</v>
+        <v>31.2134395820038</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6821661129094115</v>
@@ -4477,7 +4477,7 @@
         <v>49.25160066809106</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28.22482975890108</v>
+        <v>28.22482974716018</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.124858103722098</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.90329296354427</v>
+        <v>54.90329291020795</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.85910698199929</v>
+        <v>13.85910704982663</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.8783620724009343</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.7220041971543966</v>
+        <v>0.7220041974659503</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>60.60189852930529</v>
+        <v>60.60189856285264</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.80902833913673</v>
+        <v>22.80902829803387</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.9252557792963276</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1824250914054827</v>
+        <v>0.1824250913164777</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>51.58571126071509</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>32.65780062106543</v>
+        <v>32.65780060819775</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.5389205543826759</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0470664700138391</v>
+        <v>-0.0470664699804588</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>521.6843918498166</v>
+        <v>521.6843918498165</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>49.6</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.38526398126483</v>
+        <v>48.38526400253084</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>34.41571799917731</v>
+        <v>34.41571805743106</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.3026979889460776</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1756035932822492</v>
+        <v>-0.1756035933045054</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.36772537039701</v>
+        <v>49.36772548114097</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>27.0997900198229</v>
+        <v>27.09979002349502</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.5201960900467223</v>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>507.8444355676941</v>
+        <v>507.8444355676966</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>41.8</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>59.70459344154899</v>
+        <v>59.70459350693153</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.95547633483103</v>
+        <v>13.95547634384353</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.250867335614468</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1810026955600994</v>
+        <v>0.1810026954933337</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.19507220423252</v>
+        <v>52.19507227441591</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.65990355057724</v>
+        <v>12.65990358051635</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.6191517937938765</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.3209853448931216</v>
+        <v>0.3209853451156611</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.649508785388</v>
+        <v>51.64950856939405</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.39842400647319</v>
+        <v>18.39842419649558</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.3794811507416541</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1113588164441787</v>
+        <v>0.1113588171118015</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.65573194439048</v>
+        <v>45.65573206385948</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>25.60104852329613</v>
+        <v>25.60104858446784</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.2889608618431269</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.3298249224320805</v>
+        <v>-0.3298249224654724</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>58.94982205557975</v>
+        <v>58.94982202494404</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.09051244175178</v>
+        <v>18.09051245357838</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.7926827604334864</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>2.263092228398176</v>
+        <v>2.26309222850945</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>49.19890133100287</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.98307793401825</v>
+        <v>27.9830779840957</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.3753585890398632</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.88149446316604</v>
+        <v>46.88149429544475</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.14945181842516</v>
+        <v>20.14945181668812</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.295609292796624</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1108843054902433</v>
+        <v>0.1108843058463127</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.8122191991387</v>
+        <v>53.81221918272522</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.98096650937949</v>
+        <v>17.98096647277624</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.4237673457920807</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1015492915440932</v>
+        <v>-0.1015492914734612</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>465.9103873813396</v>
+        <v>465.9103873813388</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>22.15</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54.45207036529564</v>
+        <v>54.45207038901018</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>29.76994827861668</v>
+        <v>29.76994834446798</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.168387659332808</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0067389437749514</v>
+        <v>-0.0067389437638245</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.38752713086369</v>
+        <v>53.38752712080388</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.01141672656926</v>
+        <v>11.01141669280415</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.758796288436487</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3410747651090008</v>
+        <v>0.3410747651312751</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>460.0072129166557</v>
+        <v>460.0072129166559</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>110.5</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.281400307232</v>
+        <v>54.28140029341337</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33.33672508379848</v>
+        <v>33.33672503698065</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.5031451363217708</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.5083043098737288</v>
+        <v>-0.5083043098069444</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>453.9479781898446</v>
+        <v>453.9479781898447</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>157</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.97505430610766</v>
+        <v>48.97505431759917</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.697677374783</v>
+        <v>22.69767737478299</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.6804432915929214</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1511271515609831</v>
+        <v>-0.1511271516722701</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>50.27947884873004</v>
+        <v>50.27947900427259</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.20616145951972</v>
+        <v>18.20616142771838</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.5486327017200211</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.63830617730443</v>
+        <v>47.63830618111645</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>22.70471723554974</v>
+        <v>22.70471723667121</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.2780363333781175</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6429381625778121</v>
+        <v>-0.6429381625889504</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>48.06737927961586</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.62056331263609</v>
+        <v>17.62056334179894</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.3390641895627444</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.011429849304268</v>
+        <v>0.0114298493153942</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.08840656780885</v>
+        <v>52.08840663510149</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.78130063656162</v>
+        <v>11.78130079921442</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.070378057095349</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1695027484464995</v>
+        <v>-0.1695027473337904</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.68473597703824</v>
+        <v>48.6847360893366</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.91570461273282</v>
+        <v>14.91570466292778</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.7451925879109824</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.045112337805202</v>
+        <v>-0.0451123377718179</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>48.1703672577143</v>
+        <v>48.17036714201926</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.51210452998784</v>
+        <v>11.51210457495716</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4366762645551951</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0491251949812523</v>
+        <v>0.049125194869986</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.42495335805081</v>
+        <v>46.42495334266594</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.104543285710257</v>
+        <v>8.104543253797996</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.3776563173278241</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.5345072771993116</v>
+        <v>0.5345072773105897</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.8293786149213</v>
+        <v>51.82937862272121</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.16982552676058</v>
+        <v>12.16982558712973</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.6476695101355551</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.131054017635339</v>
+        <v>0.131054017624213</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.67681777857729</v>
+        <v>50.67681779198933</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>26.3665548128157</v>
+        <v>26.36655480098383</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.6099168589986705</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1268212015834839</v>
+        <v>0.1268212016947583</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.9738858666191</v>
+        <v>49.97388596012237</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.6462373293118</v>
+        <v>16.64623731577535</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.3593174657991511</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2595457455689678</v>
+        <v>0.2595457453686749</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.51502216475509</v>
+        <v>48.51502228679372</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>27.13784057496184</v>
+        <v>27.13784053653469</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.3587707070128833</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0228715623649415</v>
+        <v>0.0228715623426885</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>57.73157296552337</v>
+        <v>57.73157293845141</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>39.37055999853986</v>
+        <v>39.37056002209843</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.2783806282070347</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.7131639533040515</v>
+        <v>-0.7131639532817937</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>57.30937165579592</v>
+        <v>57.3093716363927</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>26.05147367241229</v>
+        <v>26.05147364755246</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.6291285620136361</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1706418059890402</v>
+        <v>0.1706418060112945</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>54.92261533321217</v>
+        <v>54.92261534460241</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>24.71221934747121</v>
+        <v>24.7122193951989</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7303268719256151</v>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>418.4677509516156</v>
+        <v>418.4677509516152</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>53.5</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.27798183385112</v>
+        <v>51.27798161019099</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>30.60806253722804</v>
+        <v>30.60806259376178</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.5579357280046308</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.06552110125494651</v>
+        <v>0.0655211016555273</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>25.8473094370114</v>
+        <v>25.84730948241926</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>23.20170648378391</v>
+        <v>23.20170646590626</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.004298944579714</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.8713996361145554</v>
+        <v>-0.8713996363259682</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.714456571095</v>
+        <v>46.71445660289884</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22.59778433124249</v>
+        <v>22.59778431824867</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.447164258059129</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0172574133644912</v>
+        <v>-0.0172574135647765</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.0284648587757</v>
+        <v>50.02846479858198</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.37458715478812</v>
+        <v>23.37458721886055</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5137929860233604</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0540217245532221</v>
+        <v>0.0540217245754772</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>401.8117380140598</v>
+        <v>401.8117380140603</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>53.3</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.33180255173658</v>
+        <v>51.33180228556079</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.91041557029057</v>
+        <v>16.91041567676697</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.6617970285298043</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.3031362547004966</v>
+        <v>0.3031362549453016</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.49045755073119</v>
+        <v>47.49045761057996</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.17048846874068</v>
+        <v>11.1704884825148</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.478352841420363</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0428716064552637</v>
+        <v>0.0428716064663911</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.16130053053652</v>
+        <v>42.16130030623205</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.3662646329971</v>
+        <v>20.36626466481017</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.346267025793898</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1683939436983196</v>
+        <v>-0.1683939436093037</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>54.18071860394543</v>
+        <v>54.18071854203684</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>42.66180058507521</v>
+        <v>42.66180060082414</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.985396946955504</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>1.460908972559454</v>
+        <v>1.46090897278199</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>35.33017269949924</v>
+        <v>35.33017284930808</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.5755603482364</v>
+        <v>20.57556032087857</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.8195590053092447</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.29786329106226</v>
+        <v>46.29786328397953</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.66646881634617</v>
+        <v>17.66646881226243</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.4434148942890911</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1535382111541383</v>
+        <v>0.153538211176392</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.0806329203919</v>
+        <v>45.08063290689906</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.00430049633937</v>
+        <v>16.00430049499971</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.054679806868169</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.225276659512061</v>
+        <v>0.2252766595343036</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>381.7962757539568</v>
+        <v>381.7962757539569</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>34</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.6723394646711</v>
+        <v>50.67234004970877</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7.882847583875161</v>
+        <v>7.882850398703663</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>5.76803586874018</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.5735860626913908</v>
+        <v>0.5735860563711852</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>379.5425614398258</v>
+        <v>379.5425614398251</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>12.85</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>58.89155703420016</v>
+        <v>58.8915571906284</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.57341760892318</v>
+        <v>19.57341766221399</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.920428471590874</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0160379289632196</v>
+        <v>0.0160379289409649</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>376.1165863814951</v>
+        <v>376.1165863815039</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>5.84</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>57.11017190365995</v>
+        <v>57.11017198278034</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.03521406941517</v>
+        <v>14.03521419537636</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.580507390686543</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0117176501678637</v>
+        <v>0.0117176501344817</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.87518721045134</v>
+        <v>45.87518723224292</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>26.63416883562056</v>
+        <v>26.63416886114977</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>1.287462745276025</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.2157265371393635</v>
+        <v>0.215726537161623</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>368.5269097423962</v>
+        <v>368.5269097423974</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>14.35</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.85318373579547</v>
+        <v>46.85318371933748</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>24.94460506885646</v>
+        <v>24.94460514593906</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.6381629137303817</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.07570748121483969</v>
+        <v>-0.07570748119258459</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>366.9887636433277</v>
+        <v>366.9887636433278</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>20.35</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>59.54895633336829</v>
+        <v>59.54895621387033</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.25480417542654</v>
+        <v>17.25480416863132</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.6617064745143563</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1236813031601053</v>
+        <v>0.1236813032268684</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>47.0812046200564</v>
+        <v>47.08120457832437</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.78831505674852</v>
+        <v>17.78831510728146</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.5328576229744313</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0031906513573818</v>
+        <v>-0.0031906513128736</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>362.8347161560706</v>
+        <v>362.8347161560704</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>89.8</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>51.1434988342663</v>
+        <v>51.14349858900552</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.74667546960629</v>
+        <v>11.74667543702346</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.582835293248582</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0236759762819908</v>
+        <v>0.0236759763265007</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.38737822700613</v>
+        <v>44.3873782411204</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>10.55833092008607</v>
+        <v>10.55833093990809</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.8241658975993592</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.123054323165333</v>
+        <v>0.1230543231096977</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>357.9965419084962</v>
+        <v>357.996541908496</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>18.9</v>
@@ -7230,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>59.00147192781249</v>
+        <v>59.0014719334419</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>24.02337481637796</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>43.79565219370864</v>
+        <v>43.79565222090288</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6.775671548879134</v>
+        <v>6.775671528668552</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.5926859604038534</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.6601567602847385</v>
+        <v>0.6601567631778082</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.98292840362738</v>
+        <v>49.98292843808201</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>18.21300404315511</v>
+        <v>18.21300398647974</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.3029707186301835</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46.47643377135237</v>
+        <v>46.47643369028471</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>23.53426168205558</v>
+        <v>23.53426168451701</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.2260057699477646</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.8995932959951608</v>
+        <v>-0.8995932956390997</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>38.63180075773519</v>
+        <v>38.63180056330119</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>19.54012202316894</v>
+        <v>19.54012206587481</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.5335407445864803</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1179219620165821</v>
+        <v>0.1179219622725007</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>347.1345179996734</v>
+        <v>347.1345179996737</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>11.45</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>51.95091787801213</v>
+        <v>51.95091788802837</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>8.036457188186887</v>
+        <v>8.036457178621333</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>1.260889693194731</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0770224865641273</v>
+        <v>0.0770224864862394</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>345.5991223977943</v>
+        <v>345.5991223977941</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>21.95</v>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>56.918594669002</v>
+        <v>56.91859464542661</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>23.83867020259427</v>
+        <v>23.8386702985116</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.8594697219134093</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.2242095701037113</v>
+        <v>0.2242095701482187</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>52.4293513233108</v>
+        <v>52.42935129772516</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>30.8145603699585</v>
+        <v>30.81456036434212</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.1835439837347988</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.0229342816658306</v>
+        <v>0.0229342816213262</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>44.85298057822025</v>
+        <v>44.85298060814979</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>23.08189828816897</v>
+        <v>23.08189828234594</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.4015996922471406</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.2080802208680061</v>
+        <v>0.2080802209125143</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>49.79393836153854</v>
+        <v>49.79393835247292</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>9.428521178312453</v>
+        <v>9.428521154451218</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.5243094935545702</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.0441972253038893</v>
+        <v>-0.0441972250368132</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>337.0085391037683</v>
+        <v>337.008539103768</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>16.7</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>41.25643914202768</v>
+        <v>41.25643949509092</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>16.54126754666534</v>
+        <v>16.54126760880719</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>1.075102551451204</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.0066796512409638</v>
+        <v>-0.0066796512632184</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.57381638017899</v>
+        <v>45.57381642770749</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>17.37982889973134</v>
+        <v>17.37982885579076</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.2721357950214394</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-1.940798121302645</v>
+        <v>-1.940798121258151</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>47.50663165205417</v>
+        <v>47.50663163943973</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>7.996476972476405</v>
+        <v>7.996476958467277</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.3087616987234658</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.5862168274504338</v>
+        <v>0.5862168275839377</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>335.67583332734</v>
+        <v>335.6758333273389</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>14.05</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>49.12958477852224</v>
+        <v>49.12958472757818</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>18.84974857730242</v>
+        <v>18.84974852779266</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.3858598503153919</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.0309054910033366</v>
+        <v>0.0309054909477019</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46.04534275783045</v>
+        <v>46.04534275231484</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.32337477170351</v>
+        <v>17.32337467617201</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.5365043057203819</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-53.60807011286556</v>
+        <v>-53.6080701120867</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>333.1681896029245</v>
+        <v>333.1681896029248</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>35.1</v>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45.13615146268742</v>
+        <v>45.1361517076623</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>16.02027049406712</v>
+        <v>16.02027038292351</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.1229158698705929</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.102673017108934</v>
+        <v>0.102673016641596</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>330.3970925520741</v>
+        <v>330.3970925520739</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>529</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>43.32994609374284</v>
+        <v>43.32994607916255</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>15.649992895771</v>
+        <v>15.6499928957568</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.5807556794623164</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-5.642297907826856</v>
+        <v>-5.642297907715568</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>47.48955835170262</v>
+        <v>47.48955838437984</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>18.53117949621436</v>
+        <v>18.53117951383451</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.2983276393039684</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.0111527648991775</v>
+        <v>-0.0111527648880501</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>46.43879356684651</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>12.31793859566326</v>
+        <v>12.31793868964819</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.473658330471138</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>39.9855799777564</v>
+        <v>39.98557992147511</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>34.18313938343775</v>
+        <v>34.18313947997864</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.6192139847116913</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0040979236208339</v>
+        <v>0.0040979236319616</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>42.11977899068273</v>
+        <v>42.11977898399471</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>21.87212448425916</v>
+        <v>21.87212449718704</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.4200245246832342</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.2407776837793986</v>
+        <v>0.2407776838461632</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>45.70751059979891</v>
+        <v>45.70751047376717</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>12.71267563483869</v>
+        <v>12.71267570524646</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.8519733630675541</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.441077904659454</v>
+        <v>-0.4410779041031254</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>52.77468970436662</v>
+        <v>52.77468967059499</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>15.52418553572049</v>
+        <v>15.52418540189785</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>1.460674283264849</v>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>305.9096510880813</v>
+        <v>305.909651088082</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>22.3</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>50.00749391715368</v>
+        <v>50.0074942543109</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>18.67083892136684</v>
+        <v>18.67083890397776</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.4926732522737466</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.180033305105013</v>
+        <v>0.1800333046265462</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>42.35714312033581</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>22.17384068872852</v>
+        <v>22.17384069646845</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0.2174009234386915</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>42.92988345768978</v>
+        <v>42.92988343966517</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>15.76283696345394</v>
+        <v>15.76283704055325</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.571671192132941</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.0146128462369426</v>
+        <v>-0.0146128461924351</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>42.49974209252884</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>21.87815293952445</v>
+        <v>21.87815328417501</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.4942439985358642</v>
@@ -8647,7 +8647,7 @@
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>295.4832750172137</v>
+        <v>295.4832750172145</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>270</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45.06314127752925</v>
+        <v>45.06314122516059</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>14.66170859448404</v>
+        <v>14.66170860676418</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.496030145088179</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.582189172451403</v>
+        <v>0.5821891730077313</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>45.26760308656569</v>
+        <v>45.26760325522569</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>15.8801310955963</v>
+        <v>15.88013106772918</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.3042759210368415</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.1211066963268883</v>
+        <v>0.121106696237866</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>295.0159469538527</v>
+        <v>295.0159469538524</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>20.2</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>40.74145062283502</v>
+        <v>40.74145068774708</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>15.69733766260092</v>
+        <v>15.69733775626036</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.5740184986880712</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.0086461612434939</v>
+        <v>0.0086461612323693</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>48.72714686097271</v>
+        <v>48.727146935228</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>28.77396024335008</v>
+        <v>28.77396033005749</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>1.808836261482356</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0246854214246922</v>
+        <v>0.0246854213690551</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>285.5963999673131</v>
+        <v>285.5963999673132</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>38.8</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>49.20575526039021</v>
+        <v>49.20575533505725</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>10.31812526424282</v>
+        <v>10.31812529951511</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.97932524966495</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.0182431014523301</v>
+        <v>-0.0182431013855597</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>43.33404095230412</v>
+        <v>43.33404103853994</v>
       </c>
       <c r="I160" s="2" t="n">
         <v>10.82065856650007</v>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>43.64292932160161</v>
+        <v>43.64292930880856</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14.56223339709116</v>
+        <v>14.56223329720754</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.4797703254074707</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.3648005644324603</v>
+        <v>0.3648005644992251</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>277.9807467383362</v>
+        <v>277.9807467383361</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>311</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>43.72484653944618</v>
+        <v>43.72484656401912</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>12.63302777673314</v>
+        <v>12.63302781661886</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.4284699608765883</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-1.942086314138621</v>
+        <v>-1.94208631402734</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>49.97179985603362</v>
+        <v>49.9717998516887</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>17.27350926039448</v>
+        <v>17.2735092438204</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.2386768137423381</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.0399617003062335</v>
+        <v>-0.0399617002906543</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>272.903187920825</v>
+        <v>272.9031879208251</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>15.8</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>41.03611114915553</v>
+        <v>41.03611106442353</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>20.0999988950579</v>
+        <v>20.09999892810063</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>1.222913540737807</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.0739200522638969</v>
+        <v>-0.0739200522109216</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>271.6782709060577</v>
+        <v>271.6782709060572</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>135</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46.19560302984972</v>
+        <v>46.19560292679321</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>17.19162570018274</v>
+        <v>17.19162555524686</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.972045504700522</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.5740223216037068</v>
+        <v>-0.574022320936085</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>43.55850989791252</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>14.95365807536804</v>
+        <v>14.95365807578247</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.3143344608870071</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.0443577123976212</v>
+        <v>-0.0443577123753668</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>50.72258444433302</v>
+        <v>50.72258445892294</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>13.64931150607238</v>
+        <v>13.64931160440104</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>0.6259952648965221</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>2.970687147575813</v>
+        <v>2.970687149356154</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>46.67619535120613</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>6.453041605432626</v>
+        <v>6.453041640361542</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.2459001766626813</v>
@@ -9389,7 +9389,7 @@
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>267.7643638055042</v>
+        <v>267.7643638055044</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>176.5</v>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>39.85459427699051</v>
+        <v>39.85459433486771</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>7.734047268038883</v>
+        <v>7.734047354357247</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.8132687948270095</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.07572018608115549</v>
+        <v>-0.07572018596987121</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>44.78916457879095</v>
+        <v>44.78916451887166</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>13.36782961912087</v>
+        <v>13.36782952597025</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.06464680011044061</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.0489651670435052</v>
+        <v>-0.0489651670101327</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>264.1705153694259</v>
+        <v>264.170515369426</v>
       </c>
       <c r="E171" s="2" t="n">
         <v>18.55</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>54.38168335236679</v>
+        <v>54.38168325639902</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>14.49687447697789</v>
+        <v>14.49687466594646</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.7613016484524722</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.1307119084582813</v>
+        <v>0.1307119085584252</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>47.39154670590759</v>
+        <v>47.39154669776228</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>17.00134590078915</v>
+        <v>17.00134588425935</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>1.995181829132206</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.1388937330766992</v>
+        <v>-0.1388937329431644</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>261.1915923965755</v>
+        <v>261.1915923965754</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>52.4</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>48.26072482753818</v>
+        <v>48.26072481773842</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>24.66940591497459</v>
+        <v>24.66940596165865</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.6529792332296629</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.3691319576666787</v>
+        <v>0.3691319577111875</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>51.08349067309661</v>
+        <v>51.08349062864378</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>18.15042997327016</v>
+        <v>18.15043005161802</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.5267471855237816</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.0652299107475138</v>
+        <v>-0.06522991069187931</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>43.13583114864292</v>
+        <v>43.13583127887139</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>36.18594860672797</v>
+        <v>36.18594870551877</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.4970363771925189</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.0887838075510467</v>
+        <v>0.0887838074063932</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>43.56983295966588</v>
+        <v>43.56983291326629</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>25.82065216537687</v>
+        <v>25.82065215427524</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.5810851980984568</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.0627217036997563</v>
+        <v>0.0627217037776462</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>248.3906632199223</v>
+        <v>248.3906632199224</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>37.85</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>40.89242074256417</v>
+        <v>40.89241972964673</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>25.86258110765038</v>
+        <v>25.86258161539498</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.5278341508844057</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.0901531141236476</v>
+        <v>0.09015311503607749</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>35.86504768141444</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>35.5621403386705</v>
+        <v>35.56214023140785</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>1.046886564675346</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.0251501072066392</v>
+        <v>0.0251501072177665</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>52.59721389319981</v>
+        <v>52.59721398804831</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>13.44019579660441</v>
+        <v>13.44019574732824</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.7013086436674785</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.041859996283408</v>
+        <v>0.0418599962589282</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>42.46186654114118</v>
+        <v>42.46186681163762</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>9.438909905660983</v>
+        <v>9.438909972835011</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.3178817055022465</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>0.3083679077869976</v>
+        <v>0.3083679072306613</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>51.61016759845739</v>
+        <v>51.61016760277264</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>5.98475244346644</v>
+        <v>5.984752490038819</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>5.445339721254356</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.173433534489352</v>
+        <v>0.1734335344448431</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>54.29863770438976</v>
+        <v>54.29863752705697</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>13.6931759231227</v>
+        <v>13.69317597540148</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.5481983745526132</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.0859768596735377</v>
+        <v>0.0859768597402968</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>236.4509140939904</v>
+        <v>236.4509140939897</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>23</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>35.76647313418464</v>
+        <v>35.76647312147948</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>28.9586661898901</v>
+        <v>28.95866618675366</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.908478849668597</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>0.0120880190974727</v>
+        <v>0.0120880191085999</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10173,41 +10173,41 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>2630</v>
+        <v>2601</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>234.6644236694675</v>
+        <v>232.8699039137718</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>46.3</v>
+        <v>5.91</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G184" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>37.4191399593828</v>
+        <v>32.07840558342976</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>12.74610741490159</v>
+        <v>24.78126978414148</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.4076717466641136</v>
+        <v>1.073534091798287</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L184" s="2" t="n">
         <v>0</v>
@@ -10216,48 +10216,48 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.1935094954124121</v>
+        <v>-0.1041450107036237</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>2601</v>
+        <v>3043</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>益航</t>
+          <t>科風</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>232.8699039137718</v>
+        <v>226.7554445610626</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>5.91</v>
+        <v>20.6</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G185" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>32.07840552986299</v>
+        <v>47.71145046166746</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>24.78126983109538</v>
+        <v>9.305390090375861</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1.073534091798287</v>
+        <v>0.4769543286900412</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
@@ -10269,31 +10269,31 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.1041450107062202</v>
+        <v>0.021540885736156</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>3043</v>
+        <v>3050</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>科風</t>
+          <t>鈺德</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>226.7554445610611</v>
+        <v>218.984969863611</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>20.6</v>
+        <v>11.5</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -10304,16 +10304,16 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>47.71145058913496</v>
+        <v>51.48917586286566</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>9.305390168773208</v>
+        <v>19.17109251229686</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.4769543286900412</v>
+        <v>0.9910641144518282</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L186" s="2" t="n">
         <v>0</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.0215408856137605</v>
+        <v>0.0399803815745464</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>3050</v>
+        <v>2762</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>鈺德</t>
+          <t>世界健身-KY</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>218.984969863611</v>
+        <v>217.6749617750667</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>11.5</v>
+        <v>79</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,16 +10357,16 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>51.48917584088885</v>
+        <v>35.82772671054894</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>19.17109230725874</v>
+        <v>12.54106867920565</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.9910641144518282</v>
+        <v>0.9010942548818665</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L187" s="2" t="n">
         <v>0</v>
@@ -10375,31 +10375,31 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.0399803815634192</v>
+        <v>-0.0363592680227741</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>2762</v>
+        <v>3018</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>世界健身-KY</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>217.6749617750666</v>
+        <v>212.0619685497002</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,13 +10410,13 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>35.8277267415755</v>
+        <v>48.83231435746043</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>12.54106871543868</v>
+        <v>7.965562481145882</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.9010942548818665</v>
+        <v>0.7080780095120344</v>
       </c>
       <c r="K188" s="2" t="n">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.0363592680672817</v>
+        <v>0.1150079513358056</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10438,21 +10438,21 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>3018</v>
+        <v>2537</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>212.0619685497002</v>
+        <v>210.6450921872505</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>48.83231427448287</v>
+        <v>52.28010632850247</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>7.9655624358996</v>
+        <v>19.3661058819572</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.7080780095120344</v>
+        <v>0.2546733899508159</v>
       </c>
       <c r="K189" s="2" t="n">
         <v>0</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.115007951313549</v>
+        <v>-0.0095376841753292</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>2537</v>
+        <v>2706</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>聯上發</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>210.6450921872513</v>
+        <v>207.9549031970725</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>52.2801062722442</v>
+        <v>34.86612439663567</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>19.36610584293786</v>
+        <v>21.39735169232607</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.2546733899508159</v>
+        <v>0.3128241851823178</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>0</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0095376841753292</v>
+        <v>-0.0100733197354351</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>2706</v>
+        <v>2485</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>第一店</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>207.9549031970724</v>
+        <v>207.8116985399516</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>12.1</v>
+        <v>39.15</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,13 +10569,13 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>34.86612435542446</v>
+        <v>43.47314717154531</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>21.39735169232606</v>
+        <v>10.56445124322466</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.3128241851823178</v>
+        <v>0.4488384159978575</v>
       </c>
       <c r="K191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.010073319724306</v>
+        <v>0.0987722358593916</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>2485</v>
+        <v>2539</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>207.8116985399516</v>
+        <v>207.2838471656833</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>39.15</v>
+        <v>34.45</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,13 +10622,13 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>43.47314717154531</v>
+        <v>39.64479956377652</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>10.56445134033725</v>
+        <v>22.28291884341842</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.4488384159978575</v>
+        <v>1.295496853376137</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.0987722358148834</v>
+        <v>0.1973509142598724</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>2539</v>
+        <v>2731</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>207.2838471656833</v>
+        <v>204.0994422181572</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>34.45</v>
+        <v>144</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>39.64479947649146</v>
+        <v>51.94442380028524</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>22.28291884341842</v>
+        <v>12.35032189813692</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>1.295496853376137</v>
+        <v>0.7223821115199547</v>
       </c>
       <c r="K193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.1973509142153646</v>
+        <v>0.358364964478034</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>2731</v>
+        <v>2913</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>204.0994422181576</v>
+        <v>203.499420338118</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>144</v>
+        <v>11.05</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>51.94442401826269</v>
+        <v>49.73472649742109</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>12.35032184695256</v>
+        <v>16.51563525285365</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.7223821115199547</v>
+        <v>0.718347127290573</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.3583649635878673</v>
+        <v>0.008613769713428801</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>2913</v>
+        <v>2812</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>農林</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>203.499420338118</v>
+        <v>202.1314565118335</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>11.05</v>
+        <v>19</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>49.73472656838773</v>
+        <v>42.83119792800876</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>16.51563521622405</v>
+        <v>14.30686880513504</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.718347127290573</v>
+        <v>0.7132675923781538</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>0.008613769668921099</v>
+        <v>-0.0144178091056609</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>2812</v>
+        <v>2705</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>202.131456511834</v>
+        <v>201.1995482303353</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>19</v>
+        <v>15.15</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,13 +10834,13 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>42.83119799910645</v>
+        <v>34.26531016728315</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>14.30686861704171</v>
+        <v>31.64489942232217</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.7132675923781538</v>
+        <v>0.5312559599216675</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>0</v>
@@ -10852,31 +10852,31 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.0144178091835507</v>
+        <v>-0.0185792152532365</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>2705</v>
+        <v>2701</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>萬企</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>201.1995482303353</v>
+        <v>199.3249747992888</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>15.15</v>
+        <v>10.25</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,13 +10887,13 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>34.26531010547117</v>
+        <v>35.48545805380404</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>31.64489943374472</v>
+        <v>17.9122322187943</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.5312559599216675</v>
+        <v>1.81821377534255</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.0185792152421115</v>
+        <v>-0.0037310734618177</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>2701</v>
+        <v>2832</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>萬企</t>
+          <t>台產</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>199.3249747992888</v>
+        <v>197.3554857080671</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>10.25</v>
+        <v>57.5</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>35.48545801213805</v>
+        <v>44.13952011857619</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>17.91223243823407</v>
+        <v>15.2108668885566</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>1.81821377534255</v>
+        <v>0.3594038178346627</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -10958,31 +10958,31 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.0037310734506911</v>
+        <v>-0.0321944986071347</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>2832</v>
+        <v>2910</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>台產</t>
+          <t>統領</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>197.3554857080668</v>
+        <v>195.07299698767</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>57.5</v>
+        <v>23.55</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,13 +10993,13 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>44.13952005150704</v>
+        <v>47.10346883600245</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>15.21086694901195</v>
+        <v>15.09069117856431</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.3594038178346627</v>
+        <v>0.2340763027948071</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0321944987215593</v>
+        <v>0.0176083630423347</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11021,21 +11021,21 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>2910</v>
+        <v>3046</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>統領</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>195.07299698767</v>
+        <v>194.7650261667224</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>23.55</v>
+        <v>53.8</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,13 +11046,13 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>47.10346881008327</v>
+        <v>44.94194009956833</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>15.09069111689901</v>
+        <v>12.28474547793459</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.2340763027948071</v>
+        <v>0.3109870550503462</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>0</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.0176083630757132</v>
+        <v>0.0984670087324111</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11074,21 +11074,21 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>3046</v>
+        <v>2712</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>遠雄來</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>194.7650261667224</v>
+        <v>193.5538170221248</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>53.8</v>
+        <v>13.35</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>44.94194026293313</v>
+        <v>44.11361130296244</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>12.28474543588354</v>
+        <v>7.490084234055434</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.3109870550503462</v>
+        <v>0.2553817022124776</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
@@ -11117,31 +11117,31 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.09846700845423451</v>
+        <v>-0.1008334848882574</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>2712</v>
+        <v>2616</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>遠雄來</t>
+          <t>山隆</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>193.5538170221248</v>
+        <v>192.70884976081</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>13.35</v>
+        <v>13.2</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>44.11361130971607</v>
+        <v>37.05388138910109</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>7.490084205232517</v>
+        <v>11.34587208495236</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.2553817022124776</v>
+        <v>0.9931541841217942</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,31 +11170,31 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.1008334848882574</v>
+        <v>-0.0064537872871082</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>2616</v>
+        <v>2904</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>山隆</t>
+          <t>匯僑</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>192.7088497608091</v>
+        <v>187.9970275400316</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>13.2</v>
+        <v>12.55</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,13 +11205,13 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>37.05388110704727</v>
+        <v>36.8054186162821</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>11.34587208495236</v>
+        <v>26.15819050435861</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.9931541841217942</v>
+        <v>0.6583939932366596</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
@@ -11223,31 +11223,31 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.006453787275981</v>
+        <v>0.0173775427758359</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>2904</v>
+        <v>2614</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>匯僑</t>
+          <t>東森</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>187.9970275400316</v>
+        <v>181.6486911239652</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>12.55</v>
+        <v>18.25</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,13 +11258,13 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>36.80541839176845</v>
+        <v>53.53862483596517</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>26.15819044067358</v>
+        <v>13.98133448504701</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.6583939932366596</v>
+        <v>0.5570884225910847</v>
       </c>
       <c r="K204" s="2" t="n">
         <v>0</v>
@@ -11276,31 +11276,31 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>0.0173775427869626</v>
+        <v>0.0364684957943873</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>2614</v>
+        <v>3078</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>東森</t>
+          <t>僑威</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>181.6486911239652</v>
+        <v>179.6961425127744</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>18.25</v>
+        <v>45.45</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,16 +11311,16 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>53.5386248579811</v>
+        <v>39.79735696087868</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>13.9813344642074</v>
+        <v>37.56607627497177</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.5570884225910847</v>
+        <v>0.2992393094662611</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" s="2" t="n">
         <v>0</v>
@@ -11329,31 +11329,31 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.0364684957832615</v>
+        <v>0.3176299909124187</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>3078</v>
+        <v>2459</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>僑威</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>179.6961425127746</v>
+        <v>178.6108977332696</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>45.45</v>
+        <v>65.2</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,16 +11364,16 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>39.79735722220075</v>
+        <v>39.13604749928031</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>37.5660759340992</v>
+        <v>17.76102630167732</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.2992393094662611</v>
+        <v>1.245047455722776</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>0</v>
@@ -11382,31 +11382,31 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>0.3176299904228228</v>
+        <v>-0.09554800459488171</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>2459</v>
+        <v>2501</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>國建</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>178.6108977332696</v>
+        <v>176.3234985183478</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>65.2</v>
+        <v>21.1</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,13 +11417,13 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>39.13604749928031</v>
+        <v>32.53970982575127</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>17.76102630622755</v>
+        <v>17.28163092120595</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>1.245047455722776</v>
+        <v>0.802913568084109</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>0</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.09554800459488171</v>
+        <v>-0.0734257286853655</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11445,21 +11445,21 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>2501</v>
+        <v>2630</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>國建</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>176.3234985183478</v>
+        <v>174.6644236694676</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>21.1</v>
+        <v>46.3</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -11470,16 +11470,16 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>32.53970974171489</v>
+        <v>37.41913955178973</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>17.28163096412397</v>
+        <v>12.74610733896401</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.802913568084109</v>
+        <v>0.4076717466641136</v>
       </c>
       <c r="K208" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L208" s="2" t="n">
         <v>0</v>
@@ -11488,11 +11488,11 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.0734257286742391</v>
+        <v>-0.1935094946112643</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
         <v>43.88657111640747</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>13.81865788620261</v>
+        <v>13.81865795513039</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.3826614728232183</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0327079473925121</v>
+        <v>0.032707947425892</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>29.72809228830972</v>
+        <v>29.72809230106889</v>
       </c>
       <c r="I210" s="2" t="n">
         <v>10.5666107256688</v>
@@ -11615,7 +11615,7 @@
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>166.0575727899005</v>
+        <v>166.0575727898998</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>20.3</v>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>31.78564330734447</v>
+        <v>31.78564338313676</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>13.68267753914041</v>
+        <v>13.68267746654021</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.2019509158175141</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.1767974479641316</v>
+        <v>-0.1767974479863876</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>50.93699110253439</v>
+        <v>50.93699119178427</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>18.5877492657956</v>
+        <v>18.58774929423788</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.4308406086998798</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.0210675086448784</v>
+        <v>0.0210675085892429</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>157.8086057266999</v>
+        <v>157.8086057266984</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>19.55</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>42.09127233424995</v>
+        <v>42.09127234690295</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>14.63116927071275</v>
+        <v>14.63116925082664</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.4295264711535195</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.0276204602795814</v>
+        <v>0.0276204602907066</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>42.92552372336893</v>
+        <v>42.92552385031126</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>18.99979331323352</v>
+        <v>18.99979324681061</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.3518089708795248</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.0068861433835256</v>
+        <v>0.006886143350146</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>41.89813904609156</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>14.0248434246046</v>
+        <v>14.02484350620734</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.8682033591026128</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>51.40905223156475</v>
+        <v>51.40905224303809</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>11.47552052240313</v>
+        <v>11.4755205270423</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>1.246427831007443</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.5371268922638065</v>
+        <v>0.537126892219297</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>50.13127799260133</v>
+        <v>50.13127788688493</v>
       </c>
       <c r="I217" s="2" t="n">
         <v>15.12158397823989</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.2518789856932057</v>
+        <v>0.2518789859157541</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>129.8060301276375</v>
+        <v>129.8060301276367</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>34.85</v>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>49.43564338622819</v>
+        <v>49.43564346837656</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>10.02768879140807</v>
+        <v>10.02768881373772</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.3325436223774075</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.0828977127819349</v>
+        <v>0.0828977127040505</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>45.59315516888431</v>
+        <v>45.59315511987725</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>16.64207866384152</v>
+        <v>16.64207868817227</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.8075433008303744</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.0163701600413878</v>
+        <v>0.0163701600636399</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>40.10747332875209</v>
+        <v>40.1074731776245</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>11.68341648401103</v>
+        <v>11.68341652153388</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.3179352463744321</v>
@@ -12145,7 +12145,7 @@
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>119.4666396361403</v>
+        <v>119.4666396361402</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>22.1</v>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>46.72162657407137</v>
+        <v>46.72162655408451</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>17.00697307755958</v>
+        <v>17.00697312294996</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.738807171614679</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.0021399113579464</v>
+        <v>-0.0021399113245613</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>117.1414522817723</v>
+        <v>117.1414522817721</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>30.9</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>45.18935731417918</v>
+        <v>45.18935720566666</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>12.79619415464154</v>
+        <v>12.79619436484454</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>1.18926602042421</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>-0.009704878052379099</v>
+        <v>-0.0097048779077296</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>41.05261633072645</v>
+        <v>41.05261628556247</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>7.967565193844907</v>
+        <v>7.967565238236285</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>1.080762414150299</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.004325574896394</v>
+        <v>-0.0043255748518838</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>48.14454273760116</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>15.65328752033381</v>
+        <v>15.65328753109328</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.2920002645023277</v>
